--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7209.048191331078</v>
+        <v>11392.7551647778</v>
       </c>
       <c r="B2" t="n">
-        <v>1935</v>
+        <v>2628</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100280.910264387</v>
+        <v>122598.6060149175</v>
       </c>
       <c r="B3" t="n">
-        <v>2877</v>
+        <v>3112</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>193352.7723374429</v>
+        <v>233804.4568650572</v>
       </c>
       <c r="B4" t="n">
-        <v>1990</v>
+        <v>1783</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>286424.6344104989</v>
+        <v>345010.3077151969</v>
       </c>
       <c r="B5" t="n">
-        <v>1136</v>
+        <v>967</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>379496.4964835548</v>
+        <v>456216.1585653366</v>
       </c>
       <c r="B6" t="n">
-        <v>717</v>
+        <v>556</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>472568.3585566108</v>
+        <v>567422.0094154764</v>
       </c>
       <c r="B7" t="n">
-        <v>435</v>
+        <v>348</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>565640.2206296667</v>
+        <v>678627.8602656161</v>
       </c>
       <c r="B8" t="n">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>658712.0827027226</v>
+        <v>789833.7111157556</v>
       </c>
       <c r="B9" t="n">
-        <v>200</v>
+        <v>139</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>751783.9447757786</v>
+        <v>901039.5619658954</v>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>844855.8068488345</v>
+        <v>1012245.412816035</v>
       </c>
       <c r="B11" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>937927.6689218904</v>
+        <v>1123451.263666175</v>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1030999.530994946</v>
+        <v>1234657.114516315</v>
       </c>
       <c r="B13" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1124071.393068002</v>
+        <v>1345862.965366454</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1217143.255141058</v>
+        <v>1457068.816216594</v>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1310215.117214114</v>
+        <v>1568274.667066734</v>
       </c>
       <c r="B16" t="n">
         <v>12</v>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1403286.97928717</v>
+        <v>1679480.517916873</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1496358.841360226</v>
+        <v>1790686.368767013</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1589430.703433282</v>
+        <v>1901892.219617153</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1682502.565506338</v>
+        <v>2013098.070467293</v>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1775574.427579394</v>
+        <v>2124303.921317432</v>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1868646.28965245</v>
+        <v>2235509.772167572</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1961718.151725506</v>
+        <v>2346715.623017712</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2054790.013798562</v>
+        <v>2457921.473867851</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
@@ -746,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2147861.875871617</v>
+        <v>2569127.324717991</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2240933.737944673</v>
+        <v>2680333.175568131</v>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2334005.600017729</v>
+        <v>2791539.026418271</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2427077.462090785</v>
+        <v>2902744.87726841</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2520149.324163841</v>
+        <v>3013950.72811855</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2613221.186236897</v>
+        <v>3125156.578968689</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2706293.048309953</v>
+        <v>3236362.429818829</v>
       </c>
       <c r="B31" t="n">
         <v>1</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2799364.910383009</v>
+        <v>3347568.280668969</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2892436.772456065</v>
+        <v>3458774.131519109</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2985508.634529121</v>
+        <v>3569979.982369248</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3078580.496602177</v>
+        <v>3681185.833219388</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3171652.358675233</v>
+        <v>3792391.684069528</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>150.580656506217</v>
+        <v>216.1212934705166</v>
       </c>
       <c r="B37" t="n">
-        <v>1823</v>
+        <v>1744</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2054.066259673536</v>
+        <v>2052.515221417241</v>
       </c>
       <c r="B38" t="n">
-        <v>3061</v>
+        <v>3032</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3957.551862840854</v>
+        <v>3888.909149363965</v>
       </c>
       <c r="B39" t="n">
-        <v>2011</v>
+        <v>1975</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5861.037466008172</v>
+        <v>5725.303077310688</v>
       </c>
       <c r="B40" t="n">
-        <v>1197</v>
+        <v>1234</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7764.523069175491</v>
+        <v>7561.697005257412</v>
       </c>
       <c r="B41" t="n">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9668.00867234281</v>
+        <v>9398.090933204136</v>
       </c>
       <c r="B42" t="n">
-        <v>424</v>
+        <v>453</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11571.49427551013</v>
+        <v>11234.48486115086</v>
       </c>
       <c r="B43" t="n">
-        <v>239</v>
+        <v>294</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>13474.97987867745</v>
+        <v>13070.87878909759</v>
       </c>
       <c r="B44" t="n">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>15378.46548184477</v>
+        <v>14907.27271704431</v>
       </c>
       <c r="B45" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>17281.95108501208</v>
+        <v>16743.66664499103</v>
       </c>
       <c r="B46" t="n">
         <v>82</v>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>19185.4366881794</v>
+        <v>18580.06057293776</v>
       </c>
       <c r="B47" t="n">
         <v>54</v>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>21088.92229134672</v>
+        <v>20416.45450088448</v>
       </c>
       <c r="B48" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>22992.40789451404</v>
+        <v>22252.84842883121</v>
       </c>
       <c r="B49" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24895.89349768136</v>
+        <v>24089.24235677793</v>
       </c>
       <c r="B50" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>26799.37910084868</v>
+        <v>25925.63628472466</v>
       </c>
       <c r="B51" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>28702.864704016</v>
+        <v>27762.03021267138</v>
       </c>
       <c r="B52" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>30606.35030718331</v>
+        <v>29598.4241406181</v>
       </c>
       <c r="B53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>32509.83591035063</v>
+        <v>31434.81806856483</v>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>34413.32151351795</v>
+        <v>33271.21199651155</v>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>36316.80711668527</v>
+        <v>35107.60592445827</v>
       </c>
       <c r="B56" t="n">
         <v>2</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>38220.29271985259</v>
+        <v>36943.999852405</v>
       </c>
       <c r="B57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>40123.77832301991</v>
+        <v>38780.39378035173</v>
       </c>
       <c r="B58" t="n">
         <v>1</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>42027.26392618722</v>
+        <v>40616.78770829845</v>
       </c>
       <c r="B59" t="n">
         <v>2</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>43930.74952935454</v>
+        <v>42453.18163624517</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>45834.23513252186</v>
+        <v>44289.57556419189</v>
       </c>
       <c r="B61" t="n">
         <v>1</v>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>47737.72073568918</v>
+        <v>46125.96949213862</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>49641.2063388565</v>
+        <v>47962.36342008534</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>51544.69194202382</v>
+        <v>49798.75734803206</v>
       </c>
       <c r="B64" t="n">
         <v>1</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>53448.17754519114</v>
+        <v>51635.15127597879</v>
       </c>
       <c r="B65" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>55351.66314835846</v>
+        <v>53471.54520392552</v>
       </c>
       <c r="B66" t="n">
         <v>0</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>57255.14875152578</v>
+        <v>55307.93913187224</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>59158.63435469309</v>
+        <v>57144.33305981896</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>61062.11995786041</v>
+        <v>58980.72698776569</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>62965.60556102773</v>
+        <v>60817.12091571241</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>64869.09116419505</v>
+        <v>62653.51484365913</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.4372380856088209</v>
+        <v>0.4162159382737085</v>
       </c>
       <c r="B72" t="n">
-        <v>5177</v>
+        <v>7180</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>22.33870628921684</v>
+        <v>39.78137029939535</v>
       </c>
       <c r="B73" t="n">
-        <v>2411</v>
+        <v>1753</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>44.24017449282485</v>
+        <v>79.14652466051699</v>
       </c>
       <c r="B74" t="n">
-        <v>1002</v>
+        <v>539</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>66.14164269643287</v>
+        <v>118.5116790216386</v>
       </c>
       <c r="B75" t="n">
-        <v>519</v>
+        <v>226</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>88.04311090004089</v>
+        <v>157.8768333827603</v>
       </c>
       <c r="B76" t="n">
-        <v>284</v>
+        <v>120</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>109.9445791036489</v>
+        <v>197.2419877438819</v>
       </c>
       <c r="B77" t="n">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131.8460473072569</v>
+        <v>236.6071421050035</v>
       </c>
       <c r="B78" t="n">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>153.7475155108649</v>
+        <v>275.9722964661252</v>
       </c>
       <c r="B79" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>175.6489837144729</v>
+        <v>315.3374508272468</v>
       </c>
       <c r="B80" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>197.5504519180809</v>
+        <v>354.7026051883685</v>
       </c>
       <c r="B81" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>219.451920121689</v>
+        <v>394.0677595494901</v>
       </c>
       <c r="B82" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>241.353388325297</v>
+        <v>433.4329139106117</v>
       </c>
       <c r="B83" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>263.254856528905</v>
+        <v>472.7980682717334</v>
       </c>
       <c r="B84" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>285.156324732513</v>
+        <v>512.1632226328551</v>
       </c>
       <c r="B85" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>307.0577929361211</v>
+        <v>551.5283769939766</v>
       </c>
       <c r="B86" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>328.9592611397291</v>
+        <v>590.8935313550983</v>
       </c>
       <c r="B87" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>350.8607293433371</v>
+        <v>630.2586857162199</v>
       </c>
       <c r="B88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>372.7621975469451</v>
+        <v>669.6238400773416</v>
       </c>
       <c r="B89" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>394.6636657505531</v>
+        <v>708.9889944384632</v>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>416.5651339541611</v>
+        <v>748.3541487995849</v>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>438.4666021577692</v>
+        <v>787.7193031607065</v>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>460.3680703613771</v>
+        <v>827.0844575218281</v>
       </c>
       <c r="B93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>482.2695385649852</v>
+        <v>866.4496118829497</v>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>504.1710067685932</v>
+        <v>905.8147662440714</v>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>526.0724749722011</v>
+        <v>945.179920605193</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>547.9739431758092</v>
+        <v>984.5450749663147</v>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>569.8754113794172</v>
+        <v>1023.910229327436</v>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>591.7768795830252</v>
+        <v>1063.275383688558</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>613.6783477866333</v>
+        <v>1102.64053804968</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>635.5798159902412</v>
+        <v>1142.005692410801</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>657.4812841938492</v>
+        <v>1181.370846771923</v>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>679.3827523974572</v>
+        <v>1220.736001133045</v>
       </c>
       <c r="B103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>701.2842206010653</v>
+        <v>1260.101155494166</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>723.1856888046733</v>
+        <v>1299.466309855288</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>745.0871570082813</v>
+        <v>1338.83146421641</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-1.38198990626604e+65</v>
+        <v>-6.776205841283918e+63</v>
       </c>
       <c r="B107" t="n">
         <v>9999</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>4.137033714340567e+66</v>
+        <v>6.514486726873851e+68</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>8.412266419307738e+66</v>
+        <v>1.302904121580612e+69</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1.268749912427491e+67</v>
+        <v>1.954359570473838e+69</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1.696273182924208e+67</v>
+        <v>2.605815019367064e+69</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2.123796453420925e+67</v>
+        <v>3.257270468260291e+69</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2.551319723917642e+67</v>
+        <v>3.908725917153518e+69</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2.978842994414359e+67</v>
+        <v>4.560181366046744e+69</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>3.406366264911076e+67</v>
+        <v>5.211636814939971e+69</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>3.833889535407793e+67</v>
+        <v>5.863092263833197e+69</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>4.261412805904511e+67</v>
+        <v>6.514547712726424e+69</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>4.688936076401228e+67</v>
+        <v>7.166003161619649e+69</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>5.116459346897944e+67</v>
+        <v>7.817458610512876e+69</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>5.543982617394661e+67</v>
+        <v>8.468914059406104e+69</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>5.971505887891379e+67</v>
+        <v>9.120369508299329e+69</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>6.399029158388096e+67</v>
+        <v>9.771824957192555e+69</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>6.826552428884813e+67</v>
+        <v>1.042328040608578e+70</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>7.25407569938153e+67</v>
+        <v>1.107473585497901e+70</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>7.681598969878247e+67</v>
+        <v>1.172619130387224e+70</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>8.109122240374964e+67</v>
+        <v>1.237764675276546e+70</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>8.536645510871682e+67</v>
+        <v>1.302910220165869e+70</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>8.964168781368399e+67</v>
+        <v>1.368055765055192e+70</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>9.391692051865116e+67</v>
+        <v>1.433201309944514e+70</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>9.819215322361833e+67</v>
+        <v>1.498346854833837e+70</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1.024673859285855e+68</v>
+        <v>1.563492399723159e+70</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1.067426186335527e+68</v>
+        <v>1.628637944612482e+70</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1.110178513385198e+68</v>
+        <v>1.693783489501805e+70</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1.15293084043487e+68</v>
+        <v>1.758929034391127e+70</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1.195683167484542e+68</v>
+        <v>1.82407457928045e+70</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1.238435494534214e+68</v>
+        <v>1.889220124169773e+70</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1.281187821583885e+68</v>
+        <v>1.954365669059095e+70</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1.323940148633557e+68</v>
+        <v>2.019511213948418e+70</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1.366692475683229e+68</v>
+        <v>2.08465675883774e+70</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1.4094448027329e+68</v>
+        <v>2.149802303727063e+70</v>
       </c>
       <c r="B140" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1.452197129782572e+68</v>
+        <v>2.214947848616386e+70</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11392.7551647778</v>
+        <v>6260.495197842158</v>
       </c>
       <c r="B2" t="n">
-        <v>2628</v>
+        <v>2532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122598.6060149175</v>
+        <v>118442.0734411027</v>
       </c>
       <c r="B3" t="n">
-        <v>3112</v>
+        <v>3157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>233804.4568650572</v>
+        <v>230623.6516843633</v>
       </c>
       <c r="B4" t="n">
-        <v>1783</v>
+        <v>1922</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>345010.3077151969</v>
+        <v>342805.2299276238</v>
       </c>
       <c r="B5" t="n">
-        <v>967</v>
+        <v>945</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>456216.1585653366</v>
+        <v>454986.8081708844</v>
       </c>
       <c r="B6" t="n">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>567422.0094154764</v>
+        <v>567168.3864141449</v>
       </c>
       <c r="B7" t="n">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>678627.8602656161</v>
+        <v>679349.9646574055</v>
       </c>
       <c r="B8" t="n">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>789833.7111157556</v>
+        <v>791531.5429006661</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>901039.5619658954</v>
+        <v>903713.1211439266</v>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1012245.412816035</v>
+        <v>1015894.699387187</v>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1123451.263666175</v>
+        <v>1128076.277630448</v>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1234657.114516315</v>
+        <v>1240257.855873708</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1345862.965366454</v>
+        <v>1352439.434116969</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1457068.816216594</v>
+        <v>1464621.012360229</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1568274.667066734</v>
+        <v>1576802.59060349</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1679480.517916873</v>
+        <v>1688984.168846751</v>
       </c>
       <c r="B17" t="n">
         <v>5</v>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1790686.368767013</v>
+        <v>1801165.747090011</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1901892.219617153</v>
+        <v>1913347.325333272</v>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2013098.070467293</v>
+        <v>2025528.903576532</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2124303.921317432</v>
+        <v>2137710.481819793</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2235509.772167572</v>
+        <v>2249892.060063053</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2346715.623017712</v>
+        <v>2362073.638306314</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2457921.473867851</v>
+        <v>2474255.216549575</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2569127.324717991</v>
+        <v>2586436.794792835</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2680333.175568131</v>
+        <v>2698618.373036096</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2791539.026418271</v>
+        <v>2810799.951279357</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2902744.87726841</v>
+        <v>2922981.529522617</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3013950.72811855</v>
+        <v>3035163.107765878</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3125156.578968689</v>
+        <v>3147344.686009138</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,10 +824,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3236362.429818829</v>
+        <v>3259526.264252399</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3347568.280668969</v>
+        <v>3371707.842495659</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3458774.131519109</v>
+        <v>3483889.42073892</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3569979.982369248</v>
+        <v>3596070.99898218</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3681185.833219388</v>
+        <v>3708252.577225441</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3792391.684069528</v>
+        <v>3820434.155468701</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>216.1212934705166</v>
+        <v>229.6301475052934</v>
       </c>
       <c r="B37" t="n">
-        <v>1744</v>
+        <v>1424</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2052.515221417241</v>
+        <v>1818.403185384514</v>
       </c>
       <c r="B38" t="n">
-        <v>3032</v>
+        <v>2607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3888.909149363965</v>
+        <v>3407.176223263735</v>
       </c>
       <c r="B39" t="n">
-        <v>1975</v>
+        <v>2060</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5725.303077310688</v>
+        <v>4995.949261142956</v>
       </c>
       <c r="B40" t="n">
-        <v>1234</v>
+        <v>1325</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7561.697005257412</v>
+        <v>6584.722299022177</v>
       </c>
       <c r="B41" t="n">
-        <v>695</v>
+        <v>827</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9398.090933204136</v>
+        <v>8173.495336901398</v>
       </c>
       <c r="B42" t="n">
-        <v>453</v>
+        <v>566</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11234.48486115086</v>
+        <v>9762.268374780619</v>
       </c>
       <c r="B43" t="n">
-        <v>294</v>
+        <v>379</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>13070.87878909759</v>
+        <v>11351.04141265984</v>
       </c>
       <c r="B44" t="n">
-        <v>169</v>
+        <v>244</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14907.27271704431</v>
+        <v>12939.81445053906</v>
       </c>
       <c r="B45" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>16743.66664499103</v>
+        <v>14528.58748841828</v>
       </c>
       <c r="B46" t="n">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>18580.06057293776</v>
+        <v>16117.3605262975</v>
       </c>
       <c r="B47" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>20416.45450088448</v>
+        <v>17706.13356417673</v>
       </c>
       <c r="B48" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>22252.84842883121</v>
+        <v>19294.90660205594</v>
       </c>
       <c r="B49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24089.24235677793</v>
+        <v>20883.67963993517</v>
       </c>
       <c r="B50" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>25925.63628472466</v>
+        <v>22472.45267781439</v>
       </c>
       <c r="B51" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>27762.03021267138</v>
+        <v>24061.22571569361</v>
       </c>
       <c r="B52" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>29598.4241406181</v>
+        <v>25649.99875357283</v>
       </c>
       <c r="B53" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>31434.81806856483</v>
+        <v>27238.77179145205</v>
       </c>
       <c r="B54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>33271.21199651155</v>
+        <v>28827.54482933127</v>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>35107.60592445827</v>
+        <v>30416.31786721049</v>
       </c>
       <c r="B56" t="n">
         <v>2</v>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>36943.999852405</v>
+        <v>32005.09090508971</v>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>38780.39378035173</v>
+        <v>33593.86394296894</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>40616.78770829845</v>
+        <v>35182.63698084816</v>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>42453.18163624517</v>
+        <v>36771.41001872738</v>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>44289.57556419189</v>
+        <v>38360.1830566066</v>
       </c>
       <c r="B61" t="n">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>46125.96949213862</v>
+        <v>39948.95609448582</v>
       </c>
       <c r="B62" t="n">
         <v>2</v>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>47962.36342008534</v>
+        <v>41537.72913236504</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>49798.75734803206</v>
+        <v>43126.50217024426</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>51635.15127597879</v>
+        <v>44715.27520812349</v>
       </c>
       <c r="B65" t="n">
         <v>0</v>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>53471.54520392552</v>
+        <v>46304.04824600271</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>55307.93913187224</v>
+        <v>47892.82128388192</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>57144.33305981896</v>
+        <v>49481.59432176115</v>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>58980.72698776569</v>
+        <v>51070.36735964037</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>60817.12091571241</v>
+        <v>52659.14039751959</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>62653.51484365913</v>
+        <v>54247.91343539881</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.4162159382737085</v>
+        <v>0.5273014312332759</v>
       </c>
       <c r="B72" t="n">
-        <v>7180</v>
+        <v>8125</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>39.78137029939535</v>
+        <v>53.72108055362722</v>
       </c>
       <c r="B73" t="n">
-        <v>1753</v>
+        <v>1240</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>79.14652466051699</v>
+        <v>106.9148596760212</v>
       </c>
       <c r="B74" t="n">
-        <v>539</v>
+        <v>353</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118.5116790216386</v>
+        <v>160.1086387984151</v>
       </c>
       <c r="B75" t="n">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>157.8768333827603</v>
+        <v>213.3024179208091</v>
       </c>
       <c r="B76" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>197.2419877438819</v>
+        <v>266.496197043203</v>
       </c>
       <c r="B77" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>236.6071421050035</v>
+        <v>319.689976165597</v>
       </c>
       <c r="B78" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>275.9722964661252</v>
+        <v>372.8837552879909</v>
       </c>
       <c r="B79" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>315.3374508272468</v>
+        <v>426.0775344103849</v>
       </c>
       <c r="B80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>354.7026051883685</v>
+        <v>479.2713135327788</v>
       </c>
       <c r="B81" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>394.0677595494901</v>
+        <v>532.4650926551727</v>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>433.4329139106117</v>
+        <v>585.6588717775667</v>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>472.7980682717334</v>
+        <v>638.8526508999606</v>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>512.1632226328551</v>
+        <v>692.0464300223546</v>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>551.5283769939766</v>
+        <v>745.2402091447485</v>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>590.8935313550983</v>
+        <v>798.4339882671425</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>630.2586857162199</v>
+        <v>851.6277673895364</v>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>669.6238400773416</v>
+        <v>904.8215465119304</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>708.9889944384632</v>
+        <v>958.0153256343243</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>748.3541487995849</v>
+        <v>1011.209104756718</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>787.7193031607065</v>
+        <v>1064.402883879112</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>827.0844575218281</v>
+        <v>1117.596663001506</v>
       </c>
       <c r="B93" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>866.4496118829497</v>
+        <v>1170.7904421239</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>905.8147662440714</v>
+        <v>1223.984221246294</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>945.179920605193</v>
+        <v>1277.178000368688</v>
       </c>
       <c r="B96" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>984.5450749663147</v>
+        <v>1330.371779491082</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1023.910229327436</v>
+        <v>1383.565558613476</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1063.275383688558</v>
+        <v>1436.75933773587</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1102.64053804968</v>
+        <v>1489.953116858264</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1142.005692410801</v>
+        <v>1543.146895980658</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1181.370846771923</v>
+        <v>1596.340675103052</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1220.736001133045</v>
+        <v>1649.534454225446</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1260.101155494166</v>
+        <v>1702.72823334784</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1299.466309855288</v>
+        <v>1755.922012470234</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1338.83146421641</v>
+        <v>1809.115791592628</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-6.776205841283918e+63</v>
+        <v>-4.59850740998172e+66</v>
       </c>
       <c r="B107" t="n">
         <v>9999</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>6.514486726873851e+68</v>
+        <v>1.746922689077496e+67</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1.302904121580612e+69</v>
+        <v>3.953696119153164e+67</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1.954359570473838e+69</v>
+        <v>6.160469549228831e+67</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2.605815019367064e+69</v>
+        <v>8.3672429793045e+67</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>3.257270468260291e+69</v>
+        <v>1.057401640938017e+68</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>3.908725917153518e+69</v>
+        <v>1.278078983945584e+68</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4.560181366046744e+69</v>
+        <v>1.49875632695315e+68</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>5.211636814939971e+69</v>
+        <v>1.719433669960717e+68</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>5.863092263833197e+69</v>
+        <v>1.940111012968284e+68</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>6.514547712726424e+69</v>
+        <v>2.16078835597585e+68</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>7.166003161619649e+69</v>
+        <v>2.381465698983417e+68</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>7.817458610512876e+69</v>
+        <v>2.602143041990984e+68</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>8.468914059406104e+69</v>
+        <v>2.822820384998551e+68</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>9.120369508299329e+69</v>
+        <v>3.043497728006118e+68</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>9.771824957192555e+69</v>
+        <v>3.264175071013685e+68</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1.042328040608578e+70</v>
+        <v>3.484852414021251e+68</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1.107473585497901e+70</v>
+        <v>3.705529757028818e+68</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1.172619130387224e+70</v>
+        <v>3.926207100036385e+68</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1.237764675276546e+70</v>
+        <v>4.146884443043952e+68</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1.302910220165869e+70</v>
+        <v>4.367561786051518e+68</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1.368055765055192e+70</v>
+        <v>4.588239129059085e+68</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1.433201309944514e+70</v>
+        <v>4.808916472066652e+68</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1.498346854833837e+70</v>
+        <v>5.029593815074219e+68</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1.563492399723159e+70</v>
+        <v>5.250271158081785e+68</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1.628637944612482e+70</v>
+        <v>5.470948501089352e+68</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1.693783489501805e+70</v>
+        <v>5.691625844096919e+68</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1.758929034391127e+70</v>
+        <v>5.912303187104486e+68</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1.82407457928045e+70</v>
+        <v>6.132980530112053e+68</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1.889220124169773e+70</v>
+        <v>6.35365787311962e+68</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1.954365669059095e+70</v>
+        <v>6.574335216127186e+68</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2.019511213948418e+70</v>
+        <v>6.795012559134753e+68</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2.08465675883774e+70</v>
+        <v>7.01568990214232e+68</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2.149802303727063e+70</v>
+        <v>7.236367245149887e+68</v>
       </c>
       <c r="B140" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2.214947848616386e+70</v>
+        <v>7.457044588157454e+68</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6260.495197842158</v>
+        <v>10328.39864330561</v>
       </c>
       <c r="B2" t="n">
-        <v>2532</v>
+        <v>2954</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118442.0734411027</v>
+        <v>129853.0147624496</v>
       </c>
       <c r="B3" t="n">
-        <v>3157</v>
+        <v>3208</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>230623.6516843633</v>
+        <v>249377.6308815936</v>
       </c>
       <c r="B4" t="n">
-        <v>1922</v>
+        <v>1755</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>342805.2299276238</v>
+        <v>368902.2470007376</v>
       </c>
       <c r="B5" t="n">
-        <v>945</v>
+        <v>881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>454986.8081708844</v>
+        <v>488426.8631198816</v>
       </c>
       <c r="B6" t="n">
-        <v>550</v>
+        <v>439</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>567168.3864141449</v>
+        <v>607951.4792390256</v>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>679349.9646574055</v>
+        <v>727476.0953581696</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>791531.5429006661</v>
+        <v>847000.7114773137</v>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>903713.1211439266</v>
+        <v>966525.3275964577</v>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1015894.699387187</v>
+        <v>1086049.943715601</v>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1128076.277630448</v>
+        <v>1205574.559834745</v>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1240257.855873708</v>
+        <v>1325099.175953889</v>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1352439.434116969</v>
+        <v>1444623.792073034</v>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1464621.012360229</v>
+        <v>1564148.408192178</v>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1576802.59060349</v>
+        <v>1683673.024311322</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1688984.168846751</v>
+        <v>1803197.640430466</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1801165.747090011</v>
+        <v>1922722.25654961</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1913347.325333272</v>
+        <v>2042246.872668754</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2025528.903576532</v>
+        <v>2161771.488787897</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2137710.481819793</v>
+        <v>2281296.104907041</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2249892.060063053</v>
+        <v>2400820.721026185</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2362073.638306314</v>
+        <v>2520345.337145329</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2474255.216549575</v>
+        <v>2639869.953264473</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2586436.794792835</v>
+        <v>2759394.569383617</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2698618.373036096</v>
+        <v>2878919.185502762</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2810799.951279357</v>
+        <v>2998443.801621906</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2922981.529522617</v>
+        <v>3117968.41774105</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3035163.107765878</v>
+        <v>3237493.033860194</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3147344.686009138</v>
+        <v>3357017.649979338</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3259526.264252399</v>
+        <v>3476542.266098482</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3371707.842495659</v>
+        <v>3596066.882217626</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3483889.42073892</v>
+        <v>3715591.49833677</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3596070.99898218</v>
+        <v>3835116.114455914</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3708252.577225441</v>
+        <v>3954640.730575058</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3820434.155468701</v>
+        <v>4074165.346694202</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>229.6301475052934</v>
+        <v>268.7977857855051</v>
       </c>
       <c r="B37" t="n">
-        <v>1424</v>
+        <v>3740</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1818.403185384514</v>
+        <v>3269.198157984504</v>
       </c>
       <c r="B38" t="n">
-        <v>2607</v>
+        <v>3410</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3407.176223263735</v>
+        <v>6269.598530183503</v>
       </c>
       <c r="B39" t="n">
-        <v>2060</v>
+        <v>1497</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4995.949261142956</v>
+        <v>9269.998902382502</v>
       </c>
       <c r="B40" t="n">
-        <v>1325</v>
+        <v>642</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6584.722299022177</v>
+        <v>12270.3992745815</v>
       </c>
       <c r="B41" t="n">
-        <v>827</v>
+        <v>309</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8173.495336901398</v>
+        <v>15270.7996467805</v>
       </c>
       <c r="B42" t="n">
-        <v>566</v>
+        <v>163</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9762.268374780619</v>
+        <v>18271.2000189795</v>
       </c>
       <c r="B43" t="n">
-        <v>379</v>
+        <v>89</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>11351.04141265984</v>
+        <v>21271.6003911785</v>
       </c>
       <c r="B44" t="n">
-        <v>244</v>
+        <v>62</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>12939.81445053906</v>
+        <v>24272.00076337749</v>
       </c>
       <c r="B45" t="n">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>14528.58748841828</v>
+        <v>27272.40113557649</v>
       </c>
       <c r="B46" t="n">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16117.3605262975</v>
+        <v>30272.80150777549</v>
       </c>
       <c r="B47" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17706.13356417673</v>
+        <v>33273.2018799745</v>
       </c>
       <c r="B48" t="n">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>19294.90660205594</v>
+        <v>36273.60225217349</v>
       </c>
       <c r="B49" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20883.67963993517</v>
+        <v>39274.00262437249</v>
       </c>
       <c r="B50" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>22472.45267781439</v>
+        <v>42274.40299657149</v>
       </c>
       <c r="B51" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>24061.22571569361</v>
+        <v>45274.80336877049</v>
       </c>
       <c r="B52" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>25649.99875357283</v>
+        <v>48275.20374096949</v>
       </c>
       <c r="B53" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>27238.77179145205</v>
+        <v>51275.60411316849</v>
       </c>
       <c r="B54" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>28827.54482933127</v>
+        <v>54276.00448536748</v>
       </c>
       <c r="B55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>30416.31786721049</v>
+        <v>57276.40485756649</v>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>32005.09090508971</v>
+        <v>60276.80522976549</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>33593.86394296894</v>
+        <v>63277.20560196448</v>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>35182.63698084816</v>
+        <v>66277.60597416348</v>
       </c>
       <c r="B59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>36771.41001872738</v>
+        <v>69278.00634636247</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>38360.1830566066</v>
+        <v>72278.40671856147</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>39948.95609448582</v>
+        <v>75278.80709076047</v>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>41537.72913236504</v>
+        <v>78279.20746295947</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>43126.50217024426</v>
+        <v>81279.60783515847</v>
       </c>
       <c r="B64" t="n">
         <v>0</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>44715.27520812349</v>
+        <v>84280.00820735747</v>
       </c>
       <c r="B65" t="n">
         <v>0</v>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>46304.04824600271</v>
+        <v>87280.40857955646</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>47892.82128388192</v>
+        <v>90280.80895175546</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>49481.59432176115</v>
+        <v>93281.20932395446</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>51070.36735964037</v>
+        <v>96281.60969615346</v>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>52659.14039751959</v>
+        <v>99282.01006835247</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>54247.91343539881</v>
+        <v>102282.4104405515</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.5273014312332759</v>
+        <v>0.248254508028444</v>
       </c>
       <c r="B72" t="n">
-        <v>8125</v>
+        <v>8399</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>53.72108055362722</v>
+        <v>59.77584099102528</v>
       </c>
       <c r="B73" t="n">
-        <v>1240</v>
+        <v>1145</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>106.9148596760212</v>
+        <v>119.3034274740221</v>
       </c>
       <c r="B74" t="n">
-        <v>353</v>
+        <v>277</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>160.1086387984151</v>
+        <v>178.8310139570189</v>
       </c>
       <c r="B75" t="n">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>213.3024179208091</v>
+        <v>238.3586004400158</v>
       </c>
       <c r="B76" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>266.496197043203</v>
+        <v>297.8861869230126</v>
       </c>
       <c r="B77" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>319.689976165597</v>
+        <v>357.4137734060094</v>
       </c>
       <c r="B78" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>372.8837552879909</v>
+        <v>416.9413598890063</v>
       </c>
       <c r="B79" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>426.0775344103849</v>
+        <v>476.4689463720031</v>
       </c>
       <c r="B80" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>479.2713135327788</v>
+        <v>535.9965328549999</v>
       </c>
       <c r="B81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>532.4650926551727</v>
+        <v>595.5241193379968</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>585.6588717775667</v>
+        <v>655.0517058209937</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>638.8526508999606</v>
+        <v>714.5792923039904</v>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>692.0464300223546</v>
+        <v>774.1068787869873</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>745.2402091447485</v>
+        <v>833.6344652699842</v>
       </c>
       <c r="B86" t="n">
         <v>0</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>798.4339882671425</v>
+        <v>893.1620517529809</v>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>851.6277673895364</v>
+        <v>952.6896382359778</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>904.8215465119304</v>
+        <v>1012.217224718975</v>
       </c>
       <c r="B89" t="n">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>958.0153256343243</v>
+        <v>1071.744811201971</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1011.209104756718</v>
+        <v>1131.272397684968</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1064.402883879112</v>
+        <v>1190.799984167965</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1117.596663001506</v>
+        <v>1250.327570650962</v>
       </c>
       <c r="B93" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1170.7904421239</v>
+        <v>1309.855157133959</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1223.984221246294</v>
+        <v>1369.382743616955</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1277.178000368688</v>
+        <v>1428.910330099952</v>
       </c>
       <c r="B96" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1330.371779491082</v>
+        <v>1488.437916582949</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1383.565558613476</v>
+        <v>1547.965503065946</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1436.75933773587</v>
+        <v>1607.493089548943</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1489.953116858264</v>
+        <v>1667.02067603194</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1543.146895980658</v>
+        <v>1726.548262514936</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1596.340675103052</v>
+        <v>1786.075848997933</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1649.534454225446</v>
+        <v>1845.60343548093</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1702.72823334784</v>
+        <v>1905.131021963927</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1755.922012470234</v>
+        <v>1964.658608446924</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1809.115791592628</v>
+        <v>2024.186194929921</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-4.59850740998172e+66</v>
+        <v>-1.274044768252731e+68</v>
       </c>
       <c r="B107" t="n">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1.746922689077496e+67</v>
+        <v>-1.235015600828899e+68</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>3.953696119153164e+67</v>
+        <v>-1.195986433405068e+68</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>6.160469549228831e+67</v>
+        <v>-1.156957265981236e+68</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>8.3672429793045e+67</v>
+        <v>-1.117928098557404e+68</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1.057401640938017e+68</v>
+        <v>-1.078898931133572e+68</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1.278078983945584e+68</v>
+        <v>-1.039869763709741e+68</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1.49875632695315e+68</v>
+        <v>-1.000840596285909e+68</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1.719433669960717e+68</v>
+        <v>-9.618114288620769e+67</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1.940111012968284e+68</v>
+        <v>-9.227822614382451e+67</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2.16078835597585e+68</v>
+        <v>-8.837530940144133e+67</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2.381465698983417e+68</v>
+        <v>-8.447239265905816e+67</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2.602143041990984e+68</v>
+        <v>-8.056947591667498e+67</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2.822820384998551e+68</v>
+        <v>-7.66665591742918e+67</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>3.043497728006118e+68</v>
+        <v>-7.276364243190862e+67</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>3.264175071013685e+68</v>
+        <v>-6.886072568952543e+67</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>3.484852414021251e+68</v>
+        <v>-6.495780894714225e+67</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3.705529757028818e+68</v>
+        <v>-6.105489220475907e+67</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3.926207100036385e+68</v>
+        <v>-5.715197546237589e+67</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>4.146884443043952e+68</v>
+        <v>-5.324905871999271e+67</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>4.367561786051518e+68</v>
+        <v>-4.934614197760953e+67</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>4.588239129059085e+68</v>
+        <v>-4.544322523522636e+67</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>4.808916472066652e+68</v>
+        <v>-4.154030849284318e+67</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>5.029593815074219e+68</v>
+        <v>-3.763739175046e+67</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>5.250271158081785e+68</v>
+        <v>-3.373447500807682e+67</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>5.470948501089352e+68</v>
+        <v>-2.983155826569363e+67</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>5.691625844096919e+68</v>
+        <v>-2.592864152331045e+67</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>5.912303187104486e+68</v>
+        <v>-2.202572478092727e+67</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>6.132980530112053e+68</v>
+        <v>-1.81228080385441e+67</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>6.35365787311962e+68</v>
+        <v>-1.421989129616092e+67</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>6.574335216127186e+68</v>
+        <v>-1.031697455377774e+67</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>6.795012559134753e+68</v>
+        <v>-6.414057811394558e+66</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>7.01568990214232e+68</v>
+        <v>-2.511141069011377e+66</v>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>9997</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>7.236367245149887e+68</v>
+        <v>1.391775673371804e+66</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>7.457044588157454e+68</v>
+        <v>5.294692415754985e+66</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10328.39864330561</v>
+        <v>10995.74771614274</v>
       </c>
       <c r="B2" t="n">
-        <v>2954</v>
+        <v>2067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129853.0147624496</v>
+        <v>103315.9334676514</v>
       </c>
       <c r="B3" t="n">
-        <v>3208</v>
+        <v>2854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>249377.6308815936</v>
+        <v>195636.1192191601</v>
       </c>
       <c r="B4" t="n">
-        <v>1755</v>
+        <v>1915</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>368902.2470007376</v>
+        <v>287956.3049706688</v>
       </c>
       <c r="B5" t="n">
-        <v>881</v>
+        <v>1189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>488426.8631198816</v>
+        <v>380276.4907221775</v>
       </c>
       <c r="B6" t="n">
-        <v>439</v>
+        <v>660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>607951.4792390256</v>
+        <v>472596.6764736862</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>417</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>727476.0953581696</v>
+        <v>564916.8622251949</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>307</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>847000.7114773137</v>
+        <v>657237.0479767036</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>966525.3275964577</v>
+        <v>749557.2337282123</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1086049.943715601</v>
+        <v>841877.419479721</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1205574.559834745</v>
+        <v>934197.6052312297</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1325099.175953889</v>
+        <v>1026517.790982738</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1444623.792073034</v>
+        <v>1118837.976734247</v>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1564148.408192178</v>
+        <v>1211158.162485756</v>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1683673.024311322</v>
+        <v>1303478.348237264</v>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1803197.640430466</v>
+        <v>1395798.533988773</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1922722.25654961</v>
+        <v>1488118.719740282</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2042246.872668754</v>
+        <v>1580438.905491791</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2161771.488787897</v>
+        <v>1672759.091243299</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2281296.104907041</v>
+        <v>1765079.276994808</v>
       </c>
       <c r="B21" t="n">
         <v>3</v>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2400820.721026185</v>
+        <v>1857399.462746317</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2520345.337145329</v>
+        <v>1949719.648497825</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2639869.953264473</v>
+        <v>2042039.834249334</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2759394.569383617</v>
+        <v>2134360.020000842</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2878919.185502762</v>
+        <v>2226680.205752351</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2998443.801621906</v>
+        <v>2319000.39150386</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3117968.41774105</v>
+        <v>2411320.577255369</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3237493.033860194</v>
+        <v>2503640.763006877</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3357017.649979338</v>
+        <v>2595960.948758386</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3476542.266098482</v>
+        <v>2688281.134509895</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3596066.882217626</v>
+        <v>2780601.320261403</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,10 +850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3715591.49833677</v>
+        <v>2872921.506012912</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3835116.114455914</v>
+        <v>2965241.691764421</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3954640.730575058</v>
+        <v>3057561.87751593</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4074165.346694202</v>
+        <v>3149882.063267438</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>268.7977857855051</v>
+        <v>277.5654546038044</v>
       </c>
       <c r="B37" t="n">
-        <v>3740</v>
+        <v>1264</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3269.198157984504</v>
+        <v>1704.449210291478</v>
       </c>
       <c r="B38" t="n">
-        <v>3410</v>
+        <v>2396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6269.598530183503</v>
+        <v>3131.332965979153</v>
       </c>
       <c r="B39" t="n">
-        <v>1497</v>
+        <v>1946</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>9269.998902382502</v>
+        <v>4558.216721666826</v>
       </c>
       <c r="B40" t="n">
-        <v>642</v>
+        <v>1352</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>12270.3992745815</v>
+        <v>5985.1004773545</v>
       </c>
       <c r="B41" t="n">
-        <v>309</v>
+        <v>972</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>15270.7996467805</v>
+        <v>7411.984233042174</v>
       </c>
       <c r="B42" t="n">
-        <v>163</v>
+        <v>589</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>18271.2000189795</v>
+        <v>8838.867988729848</v>
       </c>
       <c r="B43" t="n">
-        <v>89</v>
+        <v>438</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>21271.6003911785</v>
+        <v>10265.75174441752</v>
       </c>
       <c r="B44" t="n">
-        <v>62</v>
+        <v>303</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>24272.00076337749</v>
+        <v>11692.6355001052</v>
       </c>
       <c r="B45" t="n">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>27272.40113557649</v>
+        <v>13119.51925579287</v>
       </c>
       <c r="B46" t="n">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>30272.80150777549</v>
+        <v>14546.40301148054</v>
       </c>
       <c r="B47" t="n">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>33273.2018799745</v>
+        <v>15973.28676716822</v>
       </c>
       <c r="B48" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>36273.60225217349</v>
+        <v>17400.17052285589</v>
       </c>
       <c r="B49" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>39274.00262437249</v>
+        <v>18827.05427854357</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>42274.40299657149</v>
+        <v>20253.93803423124</v>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>45274.80336877049</v>
+        <v>21680.82178991891</v>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>48275.20374096949</v>
+        <v>23107.70554560659</v>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>51275.60411316849</v>
+        <v>24534.58930129427</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54276.00448536748</v>
+        <v>25961.47305698194</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>57276.40485756649</v>
+        <v>27388.35681266961</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>60276.80522976549</v>
+        <v>28815.24056835729</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>63277.20560196448</v>
+        <v>30242.12432404496</v>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>66277.60597416348</v>
+        <v>31669.00807973263</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>69278.00634636247</v>
+        <v>33095.89183542031</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>72278.40671856147</v>
+        <v>34522.77559110798</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>75278.80709076047</v>
+        <v>35949.65934679566</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>78279.20746295947</v>
+        <v>37376.54310248333</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>81279.60783515847</v>
+        <v>38803.42685817101</v>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>84280.00820735747</v>
+        <v>40230.31061385868</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>87280.40857955646</v>
+        <v>41657.19436954635</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>90280.80895175546</v>
+        <v>43084.07812523402</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>93281.20932395446</v>
+        <v>44510.9618809217</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>96281.60969615346</v>
+        <v>45937.84563660937</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>99282.01006835247</v>
+        <v>47364.72939229705</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>102282.4104405515</v>
+        <v>48791.61314798472</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.248254508028444</v>
+        <v>0.2173143255380339</v>
       </c>
       <c r="B72" t="n">
-        <v>8399</v>
+        <v>5972</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>59.77584099102528</v>
+        <v>27.56080346308812</v>
       </c>
       <c r="B73" t="n">
-        <v>1145</v>
+        <v>2173</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119.3034274740221</v>
+        <v>54.90429260063821</v>
       </c>
       <c r="B74" t="n">
-        <v>277</v>
+        <v>869</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>178.8310139570189</v>
+        <v>82.24778173818831</v>
       </c>
       <c r="B75" t="n">
-        <v>95</v>
+        <v>411</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>238.3586004400158</v>
+        <v>109.5912708757384</v>
       </c>
       <c r="B76" t="n">
-        <v>35</v>
+        <v>202</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>297.8861869230126</v>
+        <v>136.9347600132885</v>
       </c>
       <c r="B77" t="n">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>357.4137734060094</v>
+        <v>164.2782491508386</v>
       </c>
       <c r="B78" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>416.9413598890063</v>
+        <v>191.6217382883887</v>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>476.4689463720031</v>
+        <v>218.9652274259388</v>
       </c>
       <c r="B80" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>535.9965328549999</v>
+        <v>246.3087165634888</v>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>595.5241193379968</v>
+        <v>273.652205701039</v>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>655.0517058209937</v>
+        <v>300.995694838589</v>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>714.5792923039904</v>
+        <v>328.3391839761391</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>774.1068787869873</v>
+        <v>355.6826731136892</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>833.6344652699842</v>
+        <v>383.0261622512393</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>893.1620517529809</v>
+        <v>410.3696513887894</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>952.6896382359778</v>
+        <v>437.7131405263395</v>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1012.217224718975</v>
+        <v>465.0566296638896</v>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1071.744811201971</v>
+        <v>492.4001188014396</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1131.272397684968</v>
+        <v>519.7436079389897</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1190.799984167965</v>
+        <v>547.0870970765399</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1250.327570650962</v>
+        <v>574.4305862140899</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1309.855157133959</v>
+        <v>601.77407535164</v>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1369.382743616955</v>
+        <v>629.1175644891902</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1428.910330099952</v>
+        <v>656.4610536267402</v>
       </c>
       <c r="B96" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1488.437916582949</v>
+        <v>683.8045427642903</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1547.965503065946</v>
+        <v>711.1480319018403</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1607.493089548943</v>
+        <v>738.4915210393905</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1667.02067603194</v>
+        <v>765.8350101769406</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1726.548262514936</v>
+        <v>793.1784993144906</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1786.075848997933</v>
+        <v>820.5219884520408</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1845.60343548093</v>
+        <v>847.8654775895908</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1905.131021963927</v>
+        <v>875.2089667271409</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1964.658608446924</v>
+        <v>902.5524558646911</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2024.186194929921</v>
+        <v>929.8959450022411</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-1.274044768252731e+68</v>
+        <v>-6.496222701237613e+66</v>
       </c>
       <c r="B107" t="n">
         <v>1</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-1.235015600828899e+68</v>
+        <v>-4.932635814101197e+66</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-1.195986433405068e+68</v>
+        <v>-3.369048926964782e+66</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-1.156957265981236e+68</v>
+        <v>-1.805462039828366e+66</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-1.117928098557404e+68</v>
+        <v>-2.418751526919503e+65</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>9997</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-1.078898931133572e+68</v>
+        <v>1.321711734444465e+66</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-1.039869763709741e+68</v>
+        <v>2.885298621580882e+66</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-1.000840596285909e+68</v>
+        <v>4.448885508717298e+66</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-9.618114288620769e+67</v>
+        <v>6.012472395853713e+66</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-9.227822614382451e+67</v>
+        <v>7.576059282990129e+66</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-8.837530940144133e+67</v>
+        <v>9.139646170126545e+66</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-8.447239265905816e+67</v>
+        <v>1.070323305726296e+67</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-8.056947591667498e+67</v>
+        <v>1.226681994439938e+67</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-7.66665591742918e+67</v>
+        <v>1.383040683153579e+67</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-7.276364243190862e+67</v>
+        <v>1.539399371867221e+67</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-6.886072568952543e+67</v>
+        <v>1.695758060580862e+67</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-6.495780894714225e+67</v>
+        <v>1.852116749294504e+67</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-6.105489220475907e+67</v>
+        <v>2.008475438008146e+67</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-5.715197546237589e+67</v>
+        <v>2.164834126721787e+67</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-5.324905871999271e+67</v>
+        <v>2.321192815435429e+67</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-4.934614197760953e+67</v>
+        <v>2.47755150414907e+67</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-4.544322523522636e+67</v>
+        <v>2.633910192862712e+67</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-4.154030849284318e+67</v>
+        <v>2.790268881576353e+67</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-3.763739175046e+67</v>
+        <v>2.946627570289995e+67</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-3.373447500807682e+67</v>
+        <v>3.102986259003637e+67</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-2.983155826569363e+67</v>
+        <v>3.259344947717278e+67</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-2.592864152331045e+67</v>
+        <v>3.41570363643092e+67</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-2.202572478092727e+67</v>
+        <v>3.572062325144561e+67</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-1.81228080385441e+67</v>
+        <v>3.728421013858203e+67</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-1.421989129616092e+67</v>
+        <v>3.884779702571844e+67</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-1.031697455377774e+67</v>
+        <v>4.041138391285486e+67</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-6.414057811394558e+66</v>
+        <v>4.197497079999127e+67</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>-2.511141069011377e+66</v>
+        <v>4.353855768712769e+67</v>
       </c>
       <c r="B139" t="n">
-        <v>9997</v>
+        <v>0</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1.391775673371804e+66</v>
+        <v>4.510214457426411e+67</v>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>5.294692415754985e+66</v>
+        <v>4.666573146140052e+67</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10995.74771614274</v>
+        <v>10531.38572039055</v>
       </c>
       <c r="B2" t="n">
-        <v>2067</v>
+        <v>2568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103315.9334676514</v>
+        <v>117897.6928044786</v>
       </c>
       <c r="B3" t="n">
-        <v>2854</v>
+        <v>3035</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>195636.1192191601</v>
+        <v>225263.9998885667</v>
       </c>
       <c r="B4" t="n">
-        <v>1915</v>
+        <v>1795</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>287956.3049706688</v>
+        <v>332630.3069726547</v>
       </c>
       <c r="B5" t="n">
-        <v>1189</v>
+        <v>1007</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>380276.4907221775</v>
+        <v>439996.6140567428</v>
       </c>
       <c r="B6" t="n">
-        <v>660</v>
+        <v>578</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>472596.6764736862</v>
+        <v>547362.921140831</v>
       </c>
       <c r="B7" t="n">
-        <v>417</v>
+        <v>346</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>564916.8622251949</v>
+        <v>654729.2282249189</v>
       </c>
       <c r="B8" t="n">
-        <v>307</v>
+        <v>238</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>657237.0479767036</v>
+        <v>762095.535309007</v>
       </c>
       <c r="B9" t="n">
-        <v>187</v>
+        <v>128</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>749557.2337282123</v>
+        <v>869461.8423930951</v>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>841877.419479721</v>
+        <v>976828.1494771832</v>
       </c>
       <c r="B11" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>934197.6052312297</v>
+        <v>1084194.456561271</v>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1026517.790982738</v>
+        <v>1191560.763645359</v>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1118837.976734247</v>
+        <v>1298927.070729447</v>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1211158.162485756</v>
+        <v>1406293.377813536</v>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1303478.348237264</v>
+        <v>1513659.684897623</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1395798.533988773</v>
+        <v>1621025.991981712</v>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1488118.719740282</v>
+        <v>1728392.2990658</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1580438.905491791</v>
+        <v>1835758.606149888</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1672759.091243299</v>
+        <v>1943124.913233976</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1765079.276994808</v>
+        <v>2050491.220318064</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1857399.462746317</v>
+        <v>2157857.527402152</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1949719.648497825</v>
+        <v>2265223.83448624</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2042039.834249334</v>
+        <v>2372590.141570328</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2134360.020000842</v>
+        <v>2479956.448654416</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2226680.205752351</v>
+        <v>2587322.755738504</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2319000.39150386</v>
+        <v>2694689.062822592</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2411320.577255369</v>
+        <v>2802055.36990668</v>
       </c>
       <c r="B28" t="n">
         <v>2</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2503640.763006877</v>
+        <v>2909421.676990768</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -811,10 +811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2595960.948758386</v>
+        <v>3016787.984074856</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2688281.134509895</v>
+        <v>3124154.291158944</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2780601.320261403</v>
+        <v>3231520.598243033</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,10 +850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2872921.506012912</v>
+        <v>3338886.90532712</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2965241.691764421</v>
+        <v>3446253.212411209</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3057561.87751593</v>
+        <v>3553619.519495297</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3149882.063267438</v>
+        <v>3660985.826579385</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>277.5654546038044</v>
+        <v>338.9859933046497</v>
       </c>
       <c r="B37" t="n">
-        <v>1264</v>
+        <v>1560</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1704.449210291478</v>
+        <v>1896.099462405785</v>
       </c>
       <c r="B38" t="n">
-        <v>2396</v>
+        <v>2606</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3131.332965979153</v>
+        <v>3453.212931506921</v>
       </c>
       <c r="B39" t="n">
-        <v>1946</v>
+        <v>1994</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4558.216721666826</v>
+        <v>5010.326400608057</v>
       </c>
       <c r="B40" t="n">
-        <v>1352</v>
+        <v>1259</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5985.1004773545</v>
+        <v>6567.439869709193</v>
       </c>
       <c r="B41" t="n">
-        <v>972</v>
+        <v>859</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7411.984233042174</v>
+        <v>8124.553338810329</v>
       </c>
       <c r="B42" t="n">
-        <v>589</v>
+        <v>529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8838.867988729848</v>
+        <v>9681.666807911464</v>
       </c>
       <c r="B43" t="n">
-        <v>438</v>
+        <v>350</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>10265.75174441752</v>
+        <v>11238.7802770126</v>
       </c>
       <c r="B44" t="n">
-        <v>303</v>
+        <v>232</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>11692.6355001052</v>
+        <v>12795.89374611374</v>
       </c>
       <c r="B45" t="n">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>13119.51925579287</v>
+        <v>14353.00721521487</v>
       </c>
       <c r="B46" t="n">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>14546.40301148054</v>
+        <v>15910.12068431601</v>
       </c>
       <c r="B47" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>15973.28676716822</v>
+        <v>17467.23415341714</v>
       </c>
       <c r="B48" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>17400.17052285589</v>
+        <v>19024.34762251828</v>
       </c>
       <c r="B49" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>18827.05427854357</v>
+        <v>20581.46109161941</v>
       </c>
       <c r="B50" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20253.93803423124</v>
+        <v>22138.57456072055</v>
       </c>
       <c r="B51" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>21680.82178991891</v>
+        <v>23695.68802982169</v>
       </c>
       <c r="B52" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>23107.70554560659</v>
+        <v>25252.80149892282</v>
       </c>
       <c r="B53" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>24534.58930129427</v>
+        <v>26809.91496802396</v>
       </c>
       <c r="B54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>25961.47305698194</v>
+        <v>28367.02843712509</v>
       </c>
       <c r="B55" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>27388.35681266961</v>
+        <v>29924.14190622623</v>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>28815.24056835729</v>
+        <v>31481.25537532736</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>30242.12432404496</v>
+        <v>33038.3688444285</v>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>31669.00807973263</v>
+        <v>34595.48231352963</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>33095.89183542031</v>
+        <v>36152.59578263076</v>
       </c>
       <c r="B60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>34522.77559110798</v>
+        <v>37709.7092517319</v>
       </c>
       <c r="B61" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>35949.65934679566</v>
+        <v>39266.82272083304</v>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>37376.54310248333</v>
+        <v>40823.93618993417</v>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>38803.42685817101</v>
+        <v>42381.04965903531</v>
       </c>
       <c r="B64" t="n">
         <v>1</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>40230.31061385868</v>
+        <v>43938.16312813645</v>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>41657.19436954635</v>
+        <v>45495.27659723759</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>43084.07812523402</v>
+        <v>47052.39006633872</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>44510.9618809217</v>
+        <v>48609.50353543985</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>45937.84563660937</v>
+        <v>50166.61700454099</v>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>47364.72939229705</v>
+        <v>51723.73047364213</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>48791.61314798472</v>
+        <v>53280.84394274326</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.2173143255380339</v>
+        <v>0.2321819264874186</v>
       </c>
       <c r="B72" t="n">
-        <v>5972</v>
+        <v>7584</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>27.56080346308812</v>
+        <v>45.28692346383561</v>
       </c>
       <c r="B73" t="n">
-        <v>2173</v>
+        <v>1590</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>54.90429260063821</v>
+        <v>90.34166500118378</v>
       </c>
       <c r="B74" t="n">
-        <v>869</v>
+        <v>448</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>82.24778173818831</v>
+        <v>135.396406538532</v>
       </c>
       <c r="B75" t="n">
-        <v>411</v>
+        <v>178</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>109.5912708757384</v>
+        <v>180.4511480758802</v>
       </c>
       <c r="B76" t="n">
-        <v>202</v>
+        <v>67</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136.9347600132885</v>
+        <v>225.5058896132283</v>
       </c>
       <c r="B77" t="n">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>164.2782491508386</v>
+        <v>270.5606311505766</v>
       </c>
       <c r="B78" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>191.6217382883887</v>
+        <v>315.6153726879247</v>
       </c>
       <c r="B79" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>218.9652274259388</v>
+        <v>360.6701142252729</v>
       </c>
       <c r="B80" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>246.3087165634888</v>
+        <v>405.7248557626211</v>
       </c>
       <c r="B81" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>273.652205701039</v>
+        <v>450.7795972999693</v>
       </c>
       <c r="B82" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>300.995694838589</v>
+        <v>495.8343388373175</v>
       </c>
       <c r="B83" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>328.3391839761391</v>
+        <v>540.8890803746657</v>
       </c>
       <c r="B84" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>355.6826731136892</v>
+        <v>585.9438219120138</v>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>383.0261622512393</v>
+        <v>630.998563449362</v>
       </c>
       <c r="B86" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>410.3696513887894</v>
+        <v>676.0533049867103</v>
       </c>
       <c r="B87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>437.7131405263395</v>
+        <v>721.1080465240584</v>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>465.0566296638896</v>
+        <v>766.1627880614066</v>
       </c>
       <c r="B89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>492.4001188014396</v>
+        <v>811.2175295987548</v>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>519.7436079389897</v>
+        <v>856.272271136103</v>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>547.0870970765399</v>
+        <v>901.3270126734511</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>574.4305862140899</v>
+        <v>946.3817542107994</v>
       </c>
       <c r="B93" t="n">
         <v>1</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>601.77407535164</v>
+        <v>991.4364957481475</v>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>629.1175644891902</v>
+        <v>1036.491237285496</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>656.4610536267402</v>
+        <v>1081.545978822844</v>
       </c>
       <c r="B96" t="n">
         <v>0</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>683.8045427642903</v>
+        <v>1126.600720360192</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>711.1480319018403</v>
+        <v>1171.65546189754</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>738.4915210393905</v>
+        <v>1216.710203434888</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>765.8350101769406</v>
+        <v>1261.764944972236</v>
       </c>
       <c r="B100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>793.1784993144906</v>
+        <v>1306.819686509585</v>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>820.5219884520408</v>
+        <v>1351.874428046933</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>847.8654775895908</v>
+        <v>1396.929169584281</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>875.2089667271409</v>
+        <v>1441.983911121629</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>902.5524558646911</v>
+        <v>1487.038652658978</v>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>929.8959450022411</v>
+        <v>1532.093394196326</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-6.496222701237613e+66</v>
+        <v>-2.028197152643725e+66</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-4.932635814101197e+66</v>
+        <v>1.714874943241728e+67</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-3.369048926964782e+66</v>
+        <v>3.632569601747828e+67</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-1.805462039828366e+66</v>
+        <v>5.550264260253928e+67</v>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-2.418751526919503e+65</v>
+        <v>7.467958918760028e+67</v>
       </c>
       <c r="B111" t="n">
-        <v>9997</v>
+        <v>0</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1.321711734444465e+66</v>
+        <v>9.385653577266128e+67</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2.885298621580882e+66</v>
+        <v>1.130334823577223e+68</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4.448885508717298e+66</v>
+        <v>1.322104289427833e+68</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>6.012472395853713e+66</v>
+        <v>1.513873755278443e+68</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>7.576059282990129e+66</v>
+        <v>1.705643221129053e+68</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>9.139646170126545e+66</v>
+        <v>1.897412686979663e+68</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1.070323305726296e+67</v>
+        <v>2.089182152830273e+68</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1.226681994439938e+67</v>
+        <v>2.280951618680883e+68</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1.383040683153579e+67</v>
+        <v>2.472721084531493e+68</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1.539399371867221e+67</v>
+        <v>2.664490550382103e+68</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1.695758060580862e+67</v>
+        <v>2.856260016232713e+68</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1.852116749294504e+67</v>
+        <v>3.048029482083323e+68</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2.008475438008146e+67</v>
+        <v>3.239798947933933e+68</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2.164834126721787e+67</v>
+        <v>3.431568413784543e+68</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2.321192815435429e+67</v>
+        <v>3.623337879635153e+68</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2.47755150414907e+67</v>
+        <v>3.815107345485763e+68</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2.633910192862712e+67</v>
+        <v>4.006876811336373e+68</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2.790268881576353e+67</v>
+        <v>4.198646277186983e+68</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2.946627570289995e+67</v>
+        <v>4.390415743037593e+68</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>3.102986259003637e+67</v>
+        <v>4.582185208888203e+68</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>3.259344947717278e+67</v>
+        <v>4.773954674738813e+68</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>3.41570363643092e+67</v>
+        <v>4.965724140589423e+68</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>3.572062325144561e+67</v>
+        <v>5.157493606440033e+68</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>3.728421013858203e+67</v>
+        <v>5.349263072290642e+68</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>3.884779702571844e+67</v>
+        <v>5.541032538141253e+68</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>4.041138391285486e+67</v>
+        <v>5.732802003991863e+68</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>4.197497079999127e+67</v>
+        <v>5.924571469842473e+68</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>4.353855768712769e+67</v>
+        <v>6.116340935693083e+68</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>4.510214457426411e+67</v>
+        <v>6.308110401543693e+68</v>
       </c>
       <c r="B140" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>4.666573146140052e+67</v>
+        <v>6.499879867394303e+68</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10531.38572039055</v>
+        <v>9040.924672392228</v>
       </c>
       <c r="B2" t="n">
-        <v>2568</v>
+        <v>2230</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117897.6928044786</v>
+        <v>108688.7148154665</v>
       </c>
       <c r="B3" t="n">
-        <v>3035</v>
+        <v>2983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>225263.9998885667</v>
+        <v>208336.5049585408</v>
       </c>
       <c r="B4" t="n">
-        <v>1795</v>
+        <v>1940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>332630.3069726547</v>
+        <v>307984.2951016151</v>
       </c>
       <c r="B5" t="n">
-        <v>1007</v>
+        <v>1075</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>439996.6140567428</v>
+        <v>407632.0852446893</v>
       </c>
       <c r="B6" t="n">
-        <v>578</v>
+        <v>652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>547362.921140831</v>
+        <v>507279.8753877635</v>
       </c>
       <c r="B7" t="n">
-        <v>346</v>
+        <v>390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>654729.2282249189</v>
+        <v>606927.6655308378</v>
       </c>
       <c r="B8" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>762095.535309007</v>
+        <v>706575.4556739121</v>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>869461.8423930951</v>
+        <v>806223.2458169863</v>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>976828.1494771832</v>
+        <v>905871.0359600605</v>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1084194.456561271</v>
+        <v>1005518.826103135</v>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1191560.763645359</v>
+        <v>1105166.616246209</v>
       </c>
       <c r="B13" t="n">
         <v>33</v>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1298927.070729447</v>
+        <v>1204814.406389283</v>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1406293.377813536</v>
+        <v>1304462.196532358</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1513659.684897623</v>
+        <v>1404109.986675432</v>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1621025.991981712</v>
+        <v>1503757.776818506</v>
       </c>
       <c r="B17" t="n">
         <v>5</v>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1728392.2990658</v>
+        <v>1603405.56696158</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1835758.606149888</v>
+        <v>1703053.357104655</v>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1943124.913233976</v>
+        <v>1802701.147247729</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2050491.220318064</v>
+        <v>1902348.937390803</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2157857.527402152</v>
+        <v>2001996.727533877</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2265223.83448624</v>
+        <v>2101644.517676952</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2372590.141570328</v>
+        <v>2201292.307820026</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2479956.448654416</v>
+        <v>2300940.0979631</v>
       </c>
       <c r="B25" t="n">
         <v>3</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2587322.755738504</v>
+        <v>2400587.888106175</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2694689.062822592</v>
+        <v>2500235.678249249</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2802055.36990668</v>
+        <v>2599883.468392323</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2909421.676990768</v>
+        <v>2699531.258535397</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -811,10 +811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3016787.984074856</v>
+        <v>2799179.048678472</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3124154.291158944</v>
+        <v>2898826.838821546</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3231520.598243033</v>
+        <v>2998474.62896462</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3338886.90532712</v>
+        <v>3098122.419107694</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3446253.212411209</v>
+        <v>3197770.209250769</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3553619.519495297</v>
+        <v>3297417.999393843</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3660985.826579385</v>
+        <v>3397065.789536917</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>338.9859933046497</v>
+        <v>308.650528411915</v>
       </c>
       <c r="B37" t="n">
-        <v>1560</v>
+        <v>2023</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1896.099462405785</v>
+        <v>2191.809262175306</v>
       </c>
       <c r="B38" t="n">
-        <v>2606</v>
+        <v>2955</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3453.212931506921</v>
+        <v>4074.967995938696</v>
       </c>
       <c r="B39" t="n">
-        <v>1994</v>
+        <v>1942</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5010.326400608057</v>
+        <v>5958.126729702087</v>
       </c>
       <c r="B40" t="n">
-        <v>1259</v>
+        <v>1165</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6567.439869709193</v>
+        <v>7841.285463465478</v>
       </c>
       <c r="B41" t="n">
-        <v>859</v>
+        <v>710</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8124.553338810329</v>
+        <v>9724.44419722887</v>
       </c>
       <c r="B42" t="n">
-        <v>529</v>
+        <v>399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9681.666807911464</v>
+        <v>11607.60293099226</v>
       </c>
       <c r="B43" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>11238.7802770126</v>
+        <v>13490.76166475565</v>
       </c>
       <c r="B44" t="n">
-        <v>232</v>
+        <v>172</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>12795.89374611374</v>
+        <v>15373.92039851904</v>
       </c>
       <c r="B45" t="n">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>14353.00721521487</v>
+        <v>17257.07913228243</v>
       </c>
       <c r="B46" t="n">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>15910.12068431601</v>
+        <v>19140.23786604582</v>
       </c>
       <c r="B47" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17467.23415341714</v>
+        <v>21023.39659980921</v>
       </c>
       <c r="B48" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>19024.34762251828</v>
+        <v>22906.5553335726</v>
       </c>
       <c r="B49" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20581.46109161941</v>
+        <v>24789.71406733599</v>
       </c>
       <c r="B50" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>22138.57456072055</v>
+        <v>26672.87280109939</v>
       </c>
       <c r="B51" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>23695.68802982169</v>
+        <v>28556.03153486278</v>
       </c>
       <c r="B52" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>25252.80149892282</v>
+        <v>30439.19026862617</v>
       </c>
       <c r="B53" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>26809.91496802396</v>
+        <v>32322.34900238956</v>
       </c>
       <c r="B54" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>28367.02843712509</v>
+        <v>34205.50773615295</v>
       </c>
       <c r="B55" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>29924.14190622623</v>
+        <v>36088.66646991634</v>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>31481.25537532736</v>
+        <v>37971.82520367973</v>
       </c>
       <c r="B57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>33038.3688444285</v>
+        <v>39854.98393744312</v>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>34595.48231352963</v>
+        <v>41738.14267120651</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>36152.59578263076</v>
+        <v>43621.3014049699</v>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>37709.7092517319</v>
+        <v>45504.46013873329</v>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>39266.82272083304</v>
+        <v>47387.61887249668</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>40823.93618993417</v>
+        <v>49270.77760626007</v>
       </c>
       <c r="B63" t="n">
         <v>1</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>42381.04965903531</v>
+        <v>51153.93634002347</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>43938.16312813645</v>
+        <v>53037.09507378686</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>45495.27659723759</v>
+        <v>54920.25380755025</v>
       </c>
       <c r="B66" t="n">
         <v>0</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>47052.39006633872</v>
+        <v>56803.41254131364</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>48609.50353543985</v>
+        <v>58686.57127507703</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>50166.61700454099</v>
+        <v>60569.73000884042</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>51723.73047364213</v>
+        <v>62452.88874260381</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>53280.84394274326</v>
+        <v>64336.0474763672</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.2321819264874186</v>
+        <v>0.4312024710711801</v>
       </c>
       <c r="B72" t="n">
-        <v>7584</v>
+        <v>5701</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>45.28692346383561</v>
+        <v>25.8180464066754</v>
       </c>
       <c r="B73" t="n">
-        <v>1590</v>
+        <v>2251</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>90.34166500118378</v>
+        <v>51.20489034227961</v>
       </c>
       <c r="B74" t="n">
-        <v>448</v>
+        <v>925</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135.396406538532</v>
+        <v>76.59173427788382</v>
       </c>
       <c r="B75" t="n">
-        <v>178</v>
+        <v>441</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>180.4511480758802</v>
+        <v>101.978578213488</v>
       </c>
       <c r="B76" t="n">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>225.5058896132283</v>
+        <v>127.3654221490923</v>
       </c>
       <c r="B77" t="n">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>270.5606311505766</v>
+        <v>152.7522660846965</v>
       </c>
       <c r="B78" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>315.6153726879247</v>
+        <v>178.1391100203007</v>
       </c>
       <c r="B79" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>360.6701142252729</v>
+        <v>203.5259539559049</v>
       </c>
       <c r="B80" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>405.7248557626211</v>
+        <v>228.9127978915091</v>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>450.7795972999693</v>
+        <v>254.2996418271133</v>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>495.8343388373175</v>
+        <v>279.6864857627176</v>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>540.8890803746657</v>
+        <v>305.0733296983217</v>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>585.9438219120138</v>
+        <v>330.460173633926</v>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>630.998563449362</v>
+        <v>355.8470175695302</v>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>676.0533049867103</v>
+        <v>381.2338615051344</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>721.1080465240584</v>
+        <v>406.6207054407386</v>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>766.1627880614066</v>
+        <v>432.0075493763428</v>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>811.2175295987548</v>
+        <v>457.3943933119471</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>856.272271136103</v>
+        <v>482.7812372475512</v>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>901.3270126734511</v>
+        <v>508.1680811831555</v>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>946.3817542107994</v>
+        <v>533.5549251187597</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>991.4364957481475</v>
+        <v>558.9417690543639</v>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1036.491237285496</v>
+        <v>584.3286129899682</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1081.545978822844</v>
+        <v>609.7154569255723</v>
       </c>
       <c r="B96" t="n">
         <v>0</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1126.600720360192</v>
+        <v>635.1023008611766</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1171.65546189754</v>
+        <v>660.4891447967808</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1216.710203434888</v>
+        <v>685.8759887323849</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1261.764944972236</v>
+        <v>711.2628326679892</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1306.819686509585</v>
+        <v>736.6496766035934</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1351.874428046933</v>
+        <v>762.0365205391977</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1396.929169584281</v>
+        <v>787.4233644748018</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1441.983911121629</v>
+        <v>812.8102084104061</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1487.038652658978</v>
+        <v>838.1970523460103</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1532.093394196326</v>
+        <v>863.5838962816144</v>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-2.028197152643725e+66</v>
+        <v>-5.638377378184693e+65</v>
       </c>
       <c r="B107" t="n">
         <v>9999</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1.714874943241728e+67</v>
+        <v>7.231730470091186e+67</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>3.632569601747828e+67</v>
+        <v>1.451984471396422e+68</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>5.550264260253928e+67</v>
+        <v>2.180795895783725e+68</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>7.467958918760028e+67</v>
+        <v>2.909607320171028e+68</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>9.385653577266128e+67</v>
+        <v>3.638418744558331e+68</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1.130334823577223e+68</v>
+        <v>4.367230168945635e+68</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1.322104289427833e+68</v>
+        <v>5.096041593332939e+68</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1.513873755278443e+68</v>
+        <v>5.824853017720242e+68</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1.705643221129053e+68</v>
+        <v>6.553664442107545e+68</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1.897412686979663e+68</v>
+        <v>7.282475866494848e+68</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2.089182152830273e+68</v>
+        <v>8.011287290882152e+68</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2.280951618680883e+68</v>
+        <v>8.740098715269457e+68</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2.472721084531493e+68</v>
+        <v>9.46891013965676e+68</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2.664490550382103e+68</v>
+        <v>1.019772156404406e+69</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2.856260016232713e+68</v>
+        <v>1.092653298843137e+69</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>3.048029482083323e+68</v>
+        <v>1.165534441281867e+69</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>3.239798947933933e+68</v>
+        <v>1.238415583720597e+69</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3.431568413784543e+68</v>
+        <v>1.311296726159328e+69</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>3.623337879635153e+68</v>
+        <v>1.384177868598058e+69</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>3.815107345485763e+68</v>
+        <v>1.457059011036788e+69</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>4.006876811336373e+68</v>
+        <v>1.529940153475519e+69</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>4.198646277186983e+68</v>
+        <v>1.602821295914249e+69</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4.390415743037593e+68</v>
+        <v>1.675702438352979e+69</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>4.582185208888203e+68</v>
+        <v>1.74858358079171e+69</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>4.773954674738813e+68</v>
+        <v>1.82146472323044e+69</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>4.965724140589423e+68</v>
+        <v>1.89434586566917e+69</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>5.157493606440033e+68</v>
+        <v>1.9672270081079e+69</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>5.349263072290642e+68</v>
+        <v>2.040108150546631e+69</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>5.541032538141253e+68</v>
+        <v>2.112989292985361e+69</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>5.732802003991863e+68</v>
+        <v>2.185870435424092e+69</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>5.924571469842473e+68</v>
+        <v>2.258751577862822e+69</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>6.116340935693083e+68</v>
+        <v>2.331632720301552e+69</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>6.308110401543693e+68</v>
+        <v>2.404513862740283e+69</v>
       </c>
       <c r="B140" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>6.499879867394303e+68</v>
+        <v>2.477395005179013e+69</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9040.924672392228</v>
+        <v>11778.38329116783</v>
       </c>
       <c r="B2" t="n">
-        <v>2230</v>
+        <v>1893</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108688.7148154665</v>
+        <v>99770.68819193373</v>
       </c>
       <c r="B3" t="n">
-        <v>2983</v>
+        <v>2904</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>208336.5049585408</v>
+        <v>187762.9930926996</v>
       </c>
       <c r="B4" t="n">
-        <v>1940</v>
+        <v>1796</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>307984.2951016151</v>
+        <v>275755.2979934656</v>
       </c>
       <c r="B5" t="n">
-        <v>1075</v>
+        <v>1211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>407632.0852446893</v>
+        <v>363747.6028942314</v>
       </c>
       <c r="B6" t="n">
-        <v>652</v>
+        <v>726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>507279.8753877635</v>
+        <v>451739.9077949973</v>
       </c>
       <c r="B7" t="n">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>606927.6655308378</v>
+        <v>539732.2126957632</v>
       </c>
       <c r="B8" t="n">
-        <v>232</v>
+        <v>302</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>706575.4556739121</v>
+        <v>627724.5175965291</v>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>806223.2458169863</v>
+        <v>715716.822497295</v>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>905871.0359600605</v>
+        <v>803709.1273980609</v>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1005518.826103135</v>
+        <v>891701.4322988268</v>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1105166.616246209</v>
+        <v>979693.7371995926</v>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1204814.406389283</v>
+        <v>1067686.042100359</v>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1304462.196532358</v>
+        <v>1155678.347001125</v>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1404109.986675432</v>
+        <v>1243670.651901891</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1503757.776818506</v>
+        <v>1331662.956802656</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1603405.56696158</v>
+        <v>1419655.261703422</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1703053.357104655</v>
+        <v>1507647.566604188</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1802701.147247729</v>
+        <v>1595639.871504954</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1902348.937390803</v>
+        <v>1683632.17640572</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2001996.727533877</v>
+        <v>1771624.481306486</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2101644.517676952</v>
+        <v>1859616.786207252</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2201292.307820026</v>
+        <v>1947609.091108018</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2300940.0979631</v>
+        <v>2035601.396008783</v>
       </c>
       <c r="B25" t="n">
         <v>3</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2400587.888106175</v>
+        <v>2123593.700909549</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2500235.678249249</v>
+        <v>2211586.005810315</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2599883.468392323</v>
+        <v>2299578.310711081</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2699531.258535397</v>
+        <v>2387570.615611847</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2799179.048678472</v>
+        <v>2475562.920512613</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2898826.838821546</v>
+        <v>2563555.225413379</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2998474.62896462</v>
+        <v>2651547.530314145</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -850,10 +850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3098122.419107694</v>
+        <v>2739539.835214911</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -863,10 +863,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3197770.209250769</v>
+        <v>2827532.140115676</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3297417.999393843</v>
+        <v>2915524.445016442</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3397065.789536917</v>
+        <v>3003516.749917208</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>308.650528411915</v>
+        <v>275.2080456024323</v>
       </c>
       <c r="B37" t="n">
-        <v>2023</v>
+        <v>1636</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2191.809262175306</v>
+        <v>2020.428030729412</v>
       </c>
       <c r="B38" t="n">
-        <v>2955</v>
+        <v>2924</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4074.967995938696</v>
+        <v>3765.648015856392</v>
       </c>
       <c r="B39" t="n">
-        <v>1942</v>
+        <v>2010</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5958.126729702087</v>
+        <v>5510.868000983372</v>
       </c>
       <c r="B40" t="n">
-        <v>1165</v>
+        <v>1257</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7841.285463465478</v>
+        <v>7256.087986110352</v>
       </c>
       <c r="B41" t="n">
-        <v>710</v>
+        <v>734</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9724.44419722887</v>
+        <v>9001.307971237333</v>
       </c>
       <c r="B42" t="n">
-        <v>399</v>
+        <v>485</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11607.60293099226</v>
+        <v>10746.52795636431</v>
       </c>
       <c r="B43" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>13490.76166475565</v>
+        <v>12491.74794149129</v>
       </c>
       <c r="B44" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>15373.92039851904</v>
+        <v>14236.96792661827</v>
       </c>
       <c r="B45" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>17257.07913228243</v>
+        <v>15982.18791174525</v>
       </c>
       <c r="B46" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>19140.23786604582</v>
+        <v>17727.40789687223</v>
       </c>
       <c r="B47" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>21023.39659980921</v>
+        <v>19472.62788199921</v>
       </c>
       <c r="B48" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>22906.5553335726</v>
+        <v>21217.84786712619</v>
       </c>
       <c r="B49" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24789.71406733599</v>
+        <v>22963.06785225317</v>
       </c>
       <c r="B50" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>26672.87280109939</v>
+        <v>24708.28783738015</v>
       </c>
       <c r="B51" t="n">
         <v>15</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>28556.03153486278</v>
+        <v>26453.50782250713</v>
       </c>
       <c r="B52" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>30439.19026862617</v>
+        <v>28198.72780763411</v>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>32322.34900238956</v>
+        <v>29943.94779276109</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>34205.50773615295</v>
+        <v>31689.16777788807</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>36088.66646991634</v>
+        <v>33434.38776301505</v>
       </c>
       <c r="B56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>37971.82520367973</v>
+        <v>35179.60774814204</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>39854.98393744312</v>
+        <v>36924.82773326901</v>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>41738.14267120651</v>
+        <v>38670.047718396</v>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>43621.3014049699</v>
+        <v>40415.26770352297</v>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>45504.46013873329</v>
+        <v>42160.48768864996</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>47387.61887249668</v>
+        <v>43905.70767377693</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>49270.77760626007</v>
+        <v>45650.92765890391</v>
       </c>
       <c r="B63" t="n">
         <v>1</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>51153.93634002347</v>
+        <v>47396.14764403089</v>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>53037.09507378686</v>
+        <v>49141.36762915787</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>54920.25380755025</v>
+        <v>50886.58761428485</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>56803.41254131364</v>
+        <v>52631.80759941183</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>58686.57127507703</v>
+        <v>54377.02758453881</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>60569.73000884042</v>
+        <v>56122.24756966579</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>62452.88874260381</v>
+        <v>57867.46755479278</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>64336.0474763672</v>
+        <v>59612.68753991975</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.4312024710711801</v>
+        <v>0.2321044512964187</v>
       </c>
       <c r="B72" t="n">
-        <v>5701</v>
+        <v>7184</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>25.8180464066754</v>
+        <v>38.58156003888102</v>
       </c>
       <c r="B73" t="n">
-        <v>2251</v>
+        <v>1785</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>51.20489034227961</v>
+        <v>76.93101562646562</v>
       </c>
       <c r="B74" t="n">
-        <v>925</v>
+        <v>534</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>76.59173427788382</v>
+        <v>115.2804712140502</v>
       </c>
       <c r="B75" t="n">
-        <v>441</v>
+        <v>198</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>101.978578213488</v>
+        <v>153.6299268016348</v>
       </c>
       <c r="B76" t="n">
-        <v>243</v>
+        <v>119</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127.3654221490923</v>
+        <v>191.9793823892194</v>
       </c>
       <c r="B77" t="n">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>152.7522660846965</v>
+        <v>230.328837976804</v>
       </c>
       <c r="B78" t="n">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>178.1391100203007</v>
+        <v>268.6782935643886</v>
       </c>
       <c r="B79" t="n">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>203.5259539559049</v>
+        <v>307.0277491519732</v>
       </c>
       <c r="B80" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>228.9127978915091</v>
+        <v>345.3772047395578</v>
       </c>
       <c r="B81" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>254.2996418271133</v>
+        <v>383.7266603271424</v>
       </c>
       <c r="B82" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>279.6864857627176</v>
+        <v>422.076115914727</v>
       </c>
       <c r="B83" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>305.0733296983217</v>
+        <v>460.4255715023116</v>
       </c>
       <c r="B84" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>330.460173633926</v>
+        <v>498.7750270898962</v>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>355.8470175695302</v>
+        <v>537.1244826774808</v>
       </c>
       <c r="B86" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>381.2338615051344</v>
+        <v>575.4739382650655</v>
       </c>
       <c r="B87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>406.6207054407386</v>
+        <v>613.82339385265</v>
       </c>
       <c r="B88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>432.0075493763428</v>
+        <v>652.1728494402346</v>
       </c>
       <c r="B89" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>457.3943933119471</v>
+        <v>690.5223050278192</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>482.7812372475512</v>
+        <v>728.8717606154039</v>
       </c>
       <c r="B91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>508.1680811831555</v>
+        <v>767.2212162029884</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>533.5549251187597</v>
+        <v>805.570671790573</v>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>558.9417690543639</v>
+        <v>843.9201273781576</v>
       </c>
       <c r="B94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>584.3286129899682</v>
+        <v>882.2695829657423</v>
       </c>
       <c r="B95" t="n">
         <v>1</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>609.7154569255723</v>
+        <v>920.6190385533268</v>
       </c>
       <c r="B96" t="n">
         <v>0</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>635.1023008611766</v>
+        <v>958.9684941409114</v>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>660.4891447967808</v>
+        <v>997.317949728496</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>685.8759887323849</v>
+        <v>1035.667405316081</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>711.2628326679892</v>
+        <v>1074.016860903665</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>736.6496766035934</v>
+        <v>1112.36631649125</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>762.0365205391977</v>
+        <v>1150.715772078835</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>787.4233644748018</v>
+        <v>1189.065227666419</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>812.8102084104061</v>
+        <v>1227.414683254004</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>838.1970523460103</v>
+        <v>1265.764138841588</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>863.5838962816144</v>
+        <v>1304.113594429173</v>
       </c>
       <c r="B106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-5.638377378184693e+65</v>
+        <v>-4.41589228743377e+65</v>
       </c>
       <c r="B107" t="n">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>7.231730470091186e+67</v>
+        <v>-4.163366300395377e+65</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1.451984471396422e+68</v>
+        <v>-3.910840313356985e+65</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2.180795895783725e+68</v>
+        <v>-3.658314326318592e+65</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2.909607320171028e+68</v>
+        <v>-3.405788339280199e+65</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>3.638418744558331e+68</v>
+        <v>-3.153262352241807e+65</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>4.367230168945635e+68</v>
+        <v>-2.900736365203414e+65</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>5.096041593332939e+68</v>
+        <v>-2.648210378165022e+65</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>5.824853017720242e+68</v>
+        <v>-2.395684391126629e+65</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>6.553664442107545e+68</v>
+        <v>-2.143158404088236e+65</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>7.282475866494848e+68</v>
+        <v>-1.890632417049844e+65</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>8.011287290882152e+68</v>
+        <v>-1.638106430011451e+65</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>8.740098715269457e+68</v>
+        <v>-1.385580442973058e+65</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>9.46891013965676e+68</v>
+        <v>-1.133054455934666e+65</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1.019772156404406e+69</v>
+        <v>-8.805284688962732e+64</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1.092653298843137e+69</v>
+        <v>-6.280024818578806e+64</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1.165534441281867e+69</v>
+        <v>-3.754764948194879e+64</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1.238415583720597e+69</v>
+        <v>-1.229505077810953e+64</v>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>9993</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1.311296726159328e+69</v>
+        <v>1.295754792572973e+64</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1.384177868598058e+69</v>
+        <v>3.821014662956899e+64</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1.457059011036788e+69</v>
+        <v>6.346274533340825e+64</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1.529940153475519e+69</v>
+        <v>8.871534403724751e+64</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1.602821295914249e+69</v>
+        <v>1.139679427410868e+65</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1.675702438352979e+69</v>
+        <v>1.39220541444926e+65</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1.74858358079171e+69</v>
+        <v>1.644731401487653e+65</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1.82146472323044e+69</v>
+        <v>1.897257388526046e+65</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1.89434586566917e+69</v>
+        <v>2.149783375564438e+65</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1.9672270081079e+69</v>
+        <v>2.402309362602831e+65</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2.040108150546631e+69</v>
+        <v>2.654835349641223e+65</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2.112989292985361e+69</v>
+        <v>2.907361336679616e+65</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2.185870435424092e+69</v>
+        <v>3.159887323718009e+65</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2.258751577862822e+69</v>
+        <v>3.412413310756401e+65</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2.331632720301552e+69</v>
+        <v>3.664939297794794e+65</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2.404513862740283e+69</v>
+        <v>3.917465284833187e+65</v>
       </c>
       <c r="B140" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2.477395005179013e+69</v>
+        <v>4.169991271871579e+65</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11778.38329116783</v>
+        <v>8691.78466562123</v>
       </c>
       <c r="B2" t="n">
-        <v>1893</v>
+        <v>2295</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99770.68819193373</v>
+        <v>111029.0153779166</v>
       </c>
       <c r="B3" t="n">
-        <v>2904</v>
+        <v>3073</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>187762.9930926996</v>
+        <v>213366.2460902119</v>
       </c>
       <c r="B4" t="n">
-        <v>1796</v>
+        <v>1848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>275755.2979934656</v>
+        <v>315703.4768025073</v>
       </c>
       <c r="B5" t="n">
-        <v>1211</v>
+        <v>1034</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>363747.6028942314</v>
+        <v>418040.7075148026</v>
       </c>
       <c r="B6" t="n">
-        <v>726</v>
+        <v>675</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>451739.9077949973</v>
+        <v>520377.938227098</v>
       </c>
       <c r="B7" t="n">
-        <v>450</v>
+        <v>377</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>539732.2126957632</v>
+        <v>622715.1689393934</v>
       </c>
       <c r="B8" t="n">
-        <v>302</v>
+        <v>232</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>627724.5175965291</v>
+        <v>725052.3996516886</v>
       </c>
       <c r="B9" t="n">
-        <v>217</v>
+        <v>140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>715716.822497295</v>
+        <v>827389.630363984</v>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>803709.1273980609</v>
+        <v>929726.8610762794</v>
       </c>
       <c r="B11" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>891701.4322988268</v>
+        <v>1032064.091788575</v>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>979693.7371995926</v>
+        <v>1134401.32250087</v>
       </c>
       <c r="B13" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1067686.042100359</v>
+        <v>1236738.553213165</v>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1155678.347001125</v>
+        <v>1339075.783925461</v>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1243670.651901891</v>
+        <v>1441413.014637756</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1331662.956802656</v>
+        <v>1543750.245350051</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1419655.261703422</v>
+        <v>1646087.476062347</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1507647.566604188</v>
+        <v>1748424.706774642</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1595639.871504954</v>
+        <v>1850761.937486938</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1683632.17640572</v>
+        <v>1953099.168199233</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1771624.481306486</v>
+        <v>2055436.398911528</v>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1859616.786207252</v>
+        <v>2157773.629623824</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1947609.091108018</v>
+        <v>2260110.860336119</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2035601.396008783</v>
+        <v>2362448.091048414</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2123593.700909549</v>
+        <v>2464785.32176071</v>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2211586.005810315</v>
+        <v>2567122.552473005</v>
       </c>
       <c r="B27" t="n">
         <v>2</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2299578.310711081</v>
+        <v>2669459.7831853</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2387570.615611847</v>
+        <v>2771797.013897596</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2475562.920512613</v>
+        <v>2874134.244609891</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2563555.225413379</v>
+        <v>2976471.475322186</v>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2651547.530314145</v>
+        <v>3078808.706034482</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2739539.835214911</v>
+        <v>3181145.936746777</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -863,10 +863,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2827532.140115676</v>
+        <v>3283483.167459073</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -876,10 +876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2915524.445016442</v>
+        <v>3385820.398171368</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3003516.749917208</v>
+        <v>3488157.628883663</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>275.2080456024323</v>
+        <v>223.3798477811265</v>
       </c>
       <c r="B37" t="n">
-        <v>1636</v>
+        <v>2306</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2020.428030729412</v>
+        <v>2365.672815632767</v>
       </c>
       <c r="B38" t="n">
-        <v>2924</v>
+        <v>3198</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3765.648015856392</v>
+        <v>4507.965783484407</v>
       </c>
       <c r="B39" t="n">
-        <v>2010</v>
+        <v>1957</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5510.868000983372</v>
+        <v>6650.258751336049</v>
       </c>
       <c r="B40" t="n">
-        <v>1257</v>
+        <v>1054</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7256.087986110352</v>
+        <v>8792.55171918769</v>
       </c>
       <c r="B41" t="n">
-        <v>734</v>
+        <v>564</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9001.307971237333</v>
+        <v>10934.84468703933</v>
       </c>
       <c r="B42" t="n">
-        <v>485</v>
+        <v>337</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>10746.52795636431</v>
+        <v>13077.13765489097</v>
       </c>
       <c r="B43" t="n">
-        <v>297</v>
+        <v>223</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>12491.74794149129</v>
+        <v>15219.43062274261</v>
       </c>
       <c r="B44" t="n">
-        <v>188</v>
+        <v>109</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14236.96792661827</v>
+        <v>17361.72359059425</v>
       </c>
       <c r="B45" t="n">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15982.18791174525</v>
+        <v>19504.01655844589</v>
       </c>
       <c r="B46" t="n">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>17727.40789687223</v>
+        <v>21646.30952629753</v>
       </c>
       <c r="B47" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>19472.62788199921</v>
+        <v>23788.60249414917</v>
       </c>
       <c r="B48" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>21217.84786712619</v>
+        <v>25930.89546200081</v>
       </c>
       <c r="B49" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>22963.06785225317</v>
+        <v>28073.18842985245</v>
       </c>
       <c r="B50" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>24708.28783738015</v>
+        <v>30215.48139770409</v>
       </c>
       <c r="B51" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>26453.50782250713</v>
+        <v>32357.77436555574</v>
       </c>
       <c r="B52" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>28198.72780763411</v>
+        <v>34500.06733340738</v>
       </c>
       <c r="B53" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>29943.94779276109</v>
+        <v>36642.36030125902</v>
       </c>
       <c r="B54" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>31689.16777788807</v>
+        <v>38784.65326911066</v>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>33434.38776301505</v>
+        <v>40926.9462369623</v>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>35179.60774814204</v>
+        <v>43069.23920481394</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>36924.82773326901</v>
+        <v>45211.53217266558</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>38670.047718396</v>
+        <v>47353.82514051723</v>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>40415.26770352297</v>
+        <v>49496.11810836886</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>42160.48768864996</v>
+        <v>51638.4110762205</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>43905.70767377693</v>
+        <v>53780.70404407215</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>45650.92765890391</v>
+        <v>55922.99701192378</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>47396.14764403089</v>
+        <v>58065.28997977543</v>
       </c>
       <c r="B64" t="n">
         <v>1</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>49141.36762915787</v>
+        <v>60207.58294762707</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>50886.58761428485</v>
+        <v>62349.87591547871</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>52631.80759941183</v>
+        <v>64492.16888333035</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>54377.02758453881</v>
+        <v>66634.46185118199</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>56122.24756966579</v>
+        <v>68776.75481903362</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>57867.46755479278</v>
+        <v>70919.04778688526</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>59612.68753991975</v>
+        <v>73061.3407547369</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.2321044512964187</v>
+        <v>0.4576301867187084</v>
       </c>
       <c r="B72" t="n">
-        <v>7184</v>
+        <v>6066</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>38.58156003888102</v>
+        <v>28.58143356860814</v>
       </c>
       <c r="B73" t="n">
-        <v>1785</v>
+        <v>2181</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>76.93101562646562</v>
+        <v>56.70523695049758</v>
       </c>
       <c r="B74" t="n">
-        <v>534</v>
+        <v>795</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>115.2804712140502</v>
+        <v>84.82904033238701</v>
       </c>
       <c r="B75" t="n">
-        <v>198</v>
+        <v>408</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>153.6299268016348</v>
+        <v>112.9528437142764</v>
       </c>
       <c r="B76" t="n">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>191.9793823892194</v>
+        <v>141.0766470961659</v>
       </c>
       <c r="B77" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>230.328837976804</v>
+        <v>169.2004504780553</v>
       </c>
       <c r="B78" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>268.6782935643886</v>
+        <v>197.3242538599447</v>
       </c>
       <c r="B79" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>307.0277491519732</v>
+        <v>225.4480572418342</v>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>345.3772047395578</v>
+        <v>253.5718606237236</v>
       </c>
       <c r="B81" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>383.7266603271424</v>
+        <v>281.695664005613</v>
       </c>
       <c r="B82" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>422.076115914727</v>
+        <v>309.8194673875025</v>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>460.4255715023116</v>
+        <v>337.9432707693919</v>
       </c>
       <c r="B84" t="n">
         <v>3</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>498.7750270898962</v>
+        <v>366.0670741512814</v>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>537.1244826774808</v>
+        <v>394.1908775331707</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>575.4739382650655</v>
+        <v>422.3146809150602</v>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>613.82339385265</v>
+        <v>450.4384842969496</v>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>652.1728494402346</v>
+        <v>478.5622876788391</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>690.5223050278192</v>
+        <v>506.6860910607285</v>
       </c>
       <c r="B90" t="n">
         <v>2</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>728.8717606154039</v>
+        <v>534.809894442618</v>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>767.2212162029884</v>
+        <v>562.9336978245074</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>805.570671790573</v>
+        <v>591.0575012063969</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>843.9201273781576</v>
+        <v>619.1813045882863</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>882.2695829657423</v>
+        <v>647.3051079701756</v>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>920.6190385533268</v>
+        <v>675.4289113520651</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>958.9684941409114</v>
+        <v>703.5527147339545</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>997.317949728496</v>
+        <v>731.676518115844</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1035.667405316081</v>
+        <v>759.8003214977334</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1074.016860903665</v>
+        <v>787.9241248796228</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1112.36631649125</v>
+        <v>816.0479282615123</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1150.715772078835</v>
+        <v>844.1717316434017</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1189.065227666419</v>
+        <v>872.2955350252912</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1227.414683254004</v>
+        <v>900.4193384071806</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1265.764138841588</v>
+        <v>928.54314178907</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1304.113594429173</v>
+        <v>956.6669451709595</v>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-4.41589228743377e+65</v>
+        <v>-3.036121778759075e+64</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-4.163366300395377e+65</v>
+        <v>5.733270328611999e+64</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-3.910840313356985e+65</v>
+        <v>1.450266243598307e+65</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-3.658314326318592e+65</v>
+        <v>2.327205454335415e+65</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-3.405788339280199e+65</v>
+        <v>3.204144665072522e+65</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-3.153262352241807e+65</v>
+        <v>4.08108387580963e+65</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-2.900736365203414e+65</v>
+        <v>4.958023086546737e+65</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-2.648210378165022e+65</v>
+        <v>5.834962297283844e+65</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-2.395684391126629e+65</v>
+        <v>6.711901508020952e+65</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-2.143158404088236e+65</v>
+        <v>7.58884071875806e+65</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-1.890632417049844e+65</v>
+        <v>8.465779929495168e+65</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-1.638106430011451e+65</v>
+        <v>9.342719140232274e+65</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-1.385580442973058e+65</v>
+        <v>1.021965835096938e+66</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-1.133054455934666e+65</v>
+        <v>1.109659756170649e+66</v>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-8.805284688962732e+64</v>
+        <v>1.19735367724436e+66</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-6.280024818578806e+64</v>
+        <v>1.28504759831807e+66</v>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-3.754764948194879e+64</v>
+        <v>1.372741519391781e+66</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-1.229505077810953e+64</v>
+        <v>1.460435440465492e+66</v>
       </c>
       <c r="B124" t="n">
-        <v>9993</v>
+        <v>0</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1.295754792572973e+64</v>
+        <v>1.548129361539203e+66</v>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>3.821014662956899e+64</v>
+        <v>1.635823282612913e+66</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>6.346274533340825e+64</v>
+        <v>1.723517203686624e+66</v>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>8.871534403724751e+64</v>
+        <v>1.811211124760335e+66</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1.139679427410868e+65</v>
+        <v>1.898905045834045e+66</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1.39220541444926e+65</v>
+        <v>1.986598966907756e+66</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1.644731401487653e+65</v>
+        <v>2.074292887981467e+66</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1.897257388526046e+65</v>
+        <v>2.161986809055178e+66</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2.149783375564438e+65</v>
+        <v>2.249680730128889e+66</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2.402309362602831e+65</v>
+        <v>2.337374651202599e+66</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2.654835349641223e+65</v>
+        <v>2.42506857227631e+66</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2.907361336679616e+65</v>
+        <v>2.512762493350021e+66</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>3.159887323718009e+65</v>
+        <v>2.600456414423731e+66</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>3.412413310756401e+65</v>
+        <v>2.688150335497442e+66</v>
       </c>
       <c r="B138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>3.664939297794794e+65</v>
+        <v>2.775844256571153e+66</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>3.917465284833187e+65</v>
+        <v>2.863538177644864e+66</v>
       </c>
       <c r="B140" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>4.169991271871579e+65</v>
+        <v>2.951232098718575e+66</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8691.78466562123</v>
+        <v>13098.07513341333</v>
       </c>
       <c r="B2" t="n">
-        <v>2295</v>
+        <v>2508</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111029.0153779166</v>
+        <v>118304.274997045</v>
       </c>
       <c r="B3" t="n">
-        <v>3073</v>
+        <v>2997</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>213366.2460902119</v>
+        <v>223510.4748606767</v>
       </c>
       <c r="B4" t="n">
-        <v>1848</v>
+        <v>1853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>315703.4768025073</v>
+        <v>328716.6747243083</v>
       </c>
       <c r="B5" t="n">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>418040.7075148026</v>
+        <v>433922.87458794</v>
       </c>
       <c r="B6" t="n">
-        <v>675</v>
+        <v>589</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>520377.938227098</v>
+        <v>539129.0744515717</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>622715.1689393934</v>
+        <v>644335.2743152033</v>
       </c>
       <c r="B8" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>725052.3996516886</v>
+        <v>749541.4741788351</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>827389.630363984</v>
+        <v>854747.6740424667</v>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>929726.8610762794</v>
+        <v>959953.8739060983</v>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1032064.091788575</v>
+        <v>1065160.07376973</v>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1134401.32250087</v>
+        <v>1170366.273633362</v>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1236738.553213165</v>
+        <v>1275572.473496993</v>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1339075.783925461</v>
+        <v>1380778.673360625</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1441413.014637756</v>
+        <v>1485984.873224257</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1543750.245350051</v>
+        <v>1591191.073087888</v>
       </c>
       <c r="B17" t="n">
         <v>10</v>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1646087.476062347</v>
+        <v>1696397.27295152</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1748424.706774642</v>
+        <v>1801603.472815152</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1850761.937486938</v>
+        <v>1906809.672678783</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1953099.168199233</v>
+        <v>2012015.872542415</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2055436.398911528</v>
+        <v>2117222.072406047</v>
       </c>
       <c r="B22" t="n">
         <v>2</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2157773.629623824</v>
+        <v>2222428.272269679</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2260110.860336119</v>
+        <v>2327634.472133311</v>
       </c>
       <c r="B24" t="n">
         <v>1</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2362448.091048414</v>
+        <v>2432840.671996942</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2464785.32176071</v>
+        <v>2538046.871860574</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2567122.552473005</v>
+        <v>2643253.071724205</v>
       </c>
       <c r="B27" t="n">
         <v>2</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2669459.7831853</v>
+        <v>2748459.271587837</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -798,10 +798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2771797.013897596</v>
+        <v>2853665.471451469</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2874134.244609891</v>
+        <v>2958871.671315101</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2976471.475322186</v>
+        <v>3064077.871178732</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3078808.706034482</v>
+        <v>3169284.071042364</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3181145.936746777</v>
+        <v>3274490.270905995</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3283483.167459073</v>
+        <v>3379696.470769627</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3385820.398171368</v>
+        <v>3484902.670633259</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3488157.628883663</v>
+        <v>3590108.870496891</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>223.3798477811265</v>
+        <v>172.3626942225783</v>
       </c>
       <c r="B37" t="n">
-        <v>2306</v>
+        <v>1952</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2365.672815632767</v>
+        <v>2152.970110779459</v>
       </c>
       <c r="B38" t="n">
-        <v>3198</v>
+        <v>3124</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4507.965783484407</v>
+        <v>4133.57752733634</v>
       </c>
       <c r="B39" t="n">
-        <v>1957</v>
+        <v>2013</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6650.258751336049</v>
+        <v>6114.18494389322</v>
       </c>
       <c r="B40" t="n">
-        <v>1054</v>
+        <v>1117</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>8792.55171918769</v>
+        <v>8094.792360450101</v>
       </c>
       <c r="B41" t="n">
-        <v>564</v>
+        <v>656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10934.84468703933</v>
+        <v>10075.39977700698</v>
       </c>
       <c r="B42" t="n">
-        <v>337</v>
+        <v>400</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>13077.13765489097</v>
+        <v>12056.00719356386</v>
       </c>
       <c r="B43" t="n">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>15219.43062274261</v>
+        <v>14036.61461012074</v>
       </c>
       <c r="B44" t="n">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>17361.72359059425</v>
+        <v>16017.22202667762</v>
       </c>
       <c r="B45" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>19504.01655844589</v>
+        <v>17997.8294432345</v>
       </c>
       <c r="B46" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>21646.30952629753</v>
+        <v>19978.43685979139</v>
       </c>
       <c r="B47" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>23788.60249414917</v>
+        <v>21959.04427634827</v>
       </c>
       <c r="B48" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>25930.89546200081</v>
+        <v>23939.65169290515</v>
       </c>
       <c r="B49" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>28073.18842985245</v>
+        <v>25920.25910946203</v>
       </c>
       <c r="B50" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>30215.48139770409</v>
+        <v>27900.86652601891</v>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>32357.77436555574</v>
+        <v>29881.47394257579</v>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>34500.06733340738</v>
+        <v>31862.08135913267</v>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>36642.36030125902</v>
+        <v>33842.68877568955</v>
       </c>
       <c r="B54" t="n">
         <v>3</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>38784.65326911066</v>
+        <v>35823.29619224643</v>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>40926.9462369623</v>
+        <v>37803.90360880332</v>
       </c>
       <c r="B56" t="n">
         <v>4</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>43069.23920481394</v>
+        <v>39784.5110253602</v>
       </c>
       <c r="B57" t="n">
         <v>2</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>45211.53217266558</v>
+        <v>41765.11844191707</v>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>47353.82514051723</v>
+        <v>43745.72585847396</v>
       </c>
       <c r="B59" t="n">
         <v>0</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>49496.11810836886</v>
+        <v>45726.33327503084</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>51638.4110762205</v>
+        <v>47706.94069158772</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>53780.70404407215</v>
+        <v>49687.5481081446</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>55922.99701192378</v>
+        <v>51668.15552470148</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>58065.28997977543</v>
+        <v>53648.76294125836</v>
       </c>
       <c r="B64" t="n">
         <v>1</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>60207.58294762707</v>
+        <v>55629.37035781524</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>62349.87591547871</v>
+        <v>57609.97777437212</v>
       </c>
       <c r="B66" t="n">
         <v>0</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>64492.16888333035</v>
+        <v>59590.58519092901</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>66634.46185118199</v>
+        <v>61571.19260748589</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68776.75481903362</v>
+        <v>63551.80002404276</v>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>70919.04778688526</v>
+        <v>65532.40744059964</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>73061.3407547369</v>
+        <v>67513.01485715652</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.4576301867187084</v>
+        <v>0.2693512478649214</v>
       </c>
       <c r="B72" t="n">
-        <v>6066</v>
+        <v>5983</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>28.58143356860814</v>
+        <v>27.49813949044645</v>
       </c>
       <c r="B73" t="n">
-        <v>2181</v>
+        <v>2187</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>56.70523695049758</v>
+        <v>54.72692773302798</v>
       </c>
       <c r="B74" t="n">
-        <v>795</v>
+        <v>876</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>84.82904033238701</v>
+        <v>81.95571597560951</v>
       </c>
       <c r="B75" t="n">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112.9528437142764</v>
+        <v>109.184504218191</v>
       </c>
       <c r="B76" t="n">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>141.0766470961659</v>
+        <v>136.4132924607726</v>
       </c>
       <c r="B77" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>169.2004504780553</v>
+        <v>163.6420807033541</v>
       </c>
       <c r="B78" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>197.3242538599447</v>
+        <v>190.8708689459357</v>
       </c>
       <c r="B79" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>225.4480572418342</v>
+        <v>218.0996571885172</v>
       </c>
       <c r="B80" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>253.5718606237236</v>
+        <v>245.3284454310987</v>
       </c>
       <c r="B81" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>281.695664005613</v>
+        <v>272.5572336736802</v>
       </c>
       <c r="B82" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>309.8194673875025</v>
+        <v>299.7860219162617</v>
       </c>
       <c r="B83" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>337.9432707693919</v>
+        <v>327.0148101588433</v>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>366.0670741512814</v>
+        <v>354.2435984014248</v>
       </c>
       <c r="B85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>394.1908775331707</v>
+        <v>381.4723866440063</v>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>422.3146809150602</v>
+        <v>408.7011748865879</v>
       </c>
       <c r="B87" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>450.4384842969496</v>
+        <v>435.9299631291694</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>478.5622876788391</v>
+        <v>463.1587513717509</v>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>506.6860910607285</v>
+        <v>490.3875396143324</v>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>534.809894442618</v>
+        <v>517.616327856914</v>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>562.9336978245074</v>
+        <v>544.8451160994955</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>591.0575012063969</v>
+        <v>572.0739043420771</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>619.1813045882863</v>
+        <v>599.3026925846586</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>647.3051079701756</v>
+        <v>626.5314808272401</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>675.4289113520651</v>
+        <v>653.7602690698217</v>
       </c>
       <c r="B96" t="n">
         <v>1</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>703.5527147339545</v>
+        <v>680.9890573124032</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>731.676518115844</v>
+        <v>708.2178455549847</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>759.8003214977334</v>
+        <v>735.4466337975663</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>787.9241248796228</v>
+        <v>762.6754220401479</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>816.0479282615123</v>
+        <v>789.9042102827293</v>
       </c>
       <c r="B101" t="n">
         <v>1</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>844.1717316434017</v>
+        <v>817.1329985253109</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>872.2955350252912</v>
+        <v>844.3617867678923</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>900.4193384071806</v>
+        <v>871.5905750104739</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>928.54314178907</v>
+        <v>898.8193632530555</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>956.6669451709595</v>
+        <v>926.0481514956369</v>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-3.036121778759075e+64</v>
+        <v>-4.879217183731744e+68</v>
       </c>
       <c r="B107" t="n">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>5.733270328611999e+64</v>
+        <v>-4.739769615269744e+68</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1.450266243598307e+65</v>
+        <v>-4.600322046807744e+68</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2.327205454335415e+65</v>
+        <v>-4.460874478345743e+68</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>3.204144665072522e+65</v>
+        <v>-4.321426909883743e+68</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>4.08108387580963e+65</v>
+        <v>-4.181979341421743e+68</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>4.958023086546737e+65</v>
+        <v>-4.042531772959743e+68</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>5.834962297283844e+65</v>
+        <v>-3.903084204497743e+68</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>6.711901508020952e+65</v>
+        <v>-3.763636636035743e+68</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>7.58884071875806e+65</v>
+        <v>-3.624189067573742e+68</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>8.465779929495168e+65</v>
+        <v>-3.484741499111742e+68</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>9.342719140232274e+65</v>
+        <v>-3.345293930649742e+68</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1.021965835096938e+66</v>
+        <v>-3.205846362187742e+68</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1.109659756170649e+66</v>
+        <v>-3.066398793725742e+68</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1.19735367724436e+66</v>
+        <v>-2.926951225263742e+68</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1.28504759831807e+66</v>
+        <v>-2.787503656801742e+68</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1.372741519391781e+66</v>
+        <v>-2.648056088339741e+68</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1.460435440465492e+66</v>
+        <v>-2.508608519877741e+68</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1.548129361539203e+66</v>
+        <v>-2.369160951415741e+68</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1.635823282612913e+66</v>
+        <v>-2.229713382953741e+68</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1.723517203686624e+66</v>
+        <v>-2.090265814491741e+68</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1.811211124760335e+66</v>
+        <v>-1.95081824602974e+68</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1.898905045834045e+66</v>
+        <v>-1.81137067756774e+68</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1.986598966907756e+66</v>
+        <v>-1.67192310910574e+68</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2.074292887981467e+66</v>
+        <v>-1.53247554064374e+68</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2.161986809055178e+66</v>
+        <v>-1.39302797218174e+68</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2.249680730128889e+66</v>
+        <v>-1.25358040371974e+68</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2.337374651202599e+66</v>
+        <v>-1.11413283525774e+68</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2.42506857227631e+66</v>
+        <v>-9.746852667957393e+67</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2.512762493350021e+66</v>
+        <v>-8.352376983337393e+67</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2.600456414423731e+66</v>
+        <v>-6.957901298717393e+67</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2.688150335497442e+66</v>
+        <v>-5.563425614097389e+67</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2.775844256571153e+66</v>
+        <v>-4.168949929477389e+67</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2.863538177644864e+66</v>
+        <v>-2.774474244857389e+67</v>
       </c>
       <c r="B140" t="n">
         <v>0</v>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2.951232098718575e+66</v>
+        <v>-1.379998560237389e+67</v>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>9998</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13098.07513341333</v>
+        <v>14300.05046894063</v>
       </c>
       <c r="B2" t="n">
-        <v>2508</v>
+        <v>2560</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118304.274997045</v>
+        <v>117630.3460135587</v>
       </c>
       <c r="B3" t="n">
-        <v>2997</v>
+        <v>3061</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>223510.4748606767</v>
+        <v>220960.6415581767</v>
       </c>
       <c r="B4" t="n">
-        <v>1853</v>
+        <v>1750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>328716.6747243083</v>
+        <v>324290.9371027948</v>
       </c>
       <c r="B5" t="n">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>433922.87458794</v>
+        <v>427621.2326474128</v>
       </c>
       <c r="B6" t="n">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>539129.0744515717</v>
+        <v>530951.5281920308</v>
       </c>
       <c r="B7" t="n">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>644335.2743152033</v>
+        <v>634281.8237366489</v>
       </c>
       <c r="B8" t="n">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>749541.4741788351</v>
+        <v>737612.1192812669</v>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>854747.6740424667</v>
+        <v>840942.414825885</v>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>959953.8739060983</v>
+        <v>944272.710370503</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1065160.07376973</v>
+        <v>1047603.005915121</v>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1170366.273633362</v>
+        <v>1150933.301459739</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1275572.473496993</v>
+        <v>1254263.597004357</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1380778.673360625</v>
+        <v>1357593.892548975</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1485984.873224257</v>
+        <v>1460924.188093593</v>
       </c>
       <c r="B16" t="n">
         <v>9</v>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1591191.073087888</v>
+        <v>1564254.483638211</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1696397.27295152</v>
+        <v>1667584.779182829</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1801603.472815152</v>
+        <v>1770915.074727447</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1906809.672678783</v>
+        <v>1874245.370272065</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2012015.872542415</v>
+        <v>1977575.665816683</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2117222.072406047</v>
+        <v>2080905.961361301</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2222428.272269679</v>
+        <v>2184236.256905919</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2327634.472133311</v>
+        <v>2287566.552450538</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2432840.671996942</v>
+        <v>2390896.847995156</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2538046.871860574</v>
+        <v>2494227.143539774</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2643253.071724205</v>
+        <v>2597557.439084392</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2748459.271587837</v>
+        <v>2700887.73462901</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2853665.471451469</v>
+        <v>2804218.030173628</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2958871.671315101</v>
+        <v>2907548.325718246</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3064077.871178732</v>
+        <v>3010878.621262864</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3169284.071042364</v>
+        <v>3114208.916807482</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3274490.270905995</v>
+        <v>3217539.2123521</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3379696.470769627</v>
+        <v>3320869.507896718</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3484902.670633259</v>
+        <v>3424199.803441336</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3590108.870496891</v>
+        <v>3527530.098985954</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>172.3626942225783</v>
+        <v>186.6936451040915</v>
       </c>
       <c r="B37" t="n">
-        <v>1952</v>
+        <v>1520</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2152.970110779459</v>
+        <v>1903.825012116281</v>
       </c>
       <c r="B38" t="n">
-        <v>3124</v>
+        <v>2838</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4133.57752733634</v>
+        <v>3620.95637912847</v>
       </c>
       <c r="B39" t="n">
-        <v>2013</v>
+        <v>2007</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6114.18494389322</v>
+        <v>5338.08774614066</v>
       </c>
       <c r="B40" t="n">
-        <v>1117</v>
+        <v>1284</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>8094.792360450101</v>
+        <v>7055.219113152849</v>
       </c>
       <c r="B41" t="n">
-        <v>656</v>
+        <v>781</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10075.39977700698</v>
+        <v>8772.350480165038</v>
       </c>
       <c r="B42" t="n">
-        <v>400</v>
+        <v>546</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>12056.00719356386</v>
+        <v>10489.48184717723</v>
       </c>
       <c r="B43" t="n">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>14036.61461012074</v>
+        <v>12206.61321418942</v>
       </c>
       <c r="B44" t="n">
-        <v>163</v>
+        <v>222</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16017.22202667762</v>
+        <v>13923.7445812016</v>
       </c>
       <c r="B45" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>17997.8294432345</v>
+        <v>15640.87594821379</v>
       </c>
       <c r="B46" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>19978.43685979139</v>
+        <v>17358.00731522599</v>
       </c>
       <c r="B47" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>21959.04427634827</v>
+        <v>19075.13868223818</v>
       </c>
       <c r="B48" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>23939.65169290515</v>
+        <v>20792.27004925036</v>
       </c>
       <c r="B49" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>25920.25910946203</v>
+        <v>22509.40141626255</v>
       </c>
       <c r="B50" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>27900.86652601891</v>
+        <v>24226.53278327474</v>
       </c>
       <c r="B51" t="n">
         <v>12</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>29881.47394257579</v>
+        <v>25943.66415028693</v>
       </c>
       <c r="B52" t="n">
         <v>7</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>31862.08135913267</v>
+        <v>27660.79551729912</v>
       </c>
       <c r="B53" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>33842.68877568955</v>
+        <v>29377.92688431131</v>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>35823.29619224643</v>
+        <v>31095.0582513235</v>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>37803.90360880332</v>
+        <v>32812.18961833569</v>
       </c>
       <c r="B56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>39784.5110253602</v>
+        <v>34529.32098534788</v>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>41765.11844191707</v>
+        <v>36246.45235236007</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>43745.72585847396</v>
+        <v>37963.58371937225</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>45726.33327503084</v>
+        <v>39680.71508638444</v>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>47706.94069158772</v>
+        <v>41397.84645339663</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>49687.5481081446</v>
+        <v>43114.97782040882</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>51668.15552470148</v>
+        <v>44832.10918742101</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>53648.76294125836</v>
+        <v>46549.2405544332</v>
       </c>
       <c r="B64" t="n">
         <v>1</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>55629.37035781524</v>
+        <v>48266.37192144539</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>57609.97777437212</v>
+        <v>49983.50328845758</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>59590.58519092901</v>
+        <v>51700.63465546977</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>61571.19260748589</v>
+        <v>53417.76602248196</v>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>63551.80002404276</v>
+        <v>55134.89738949414</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>65532.40744059964</v>
+        <v>56852.02875650633</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>67513.01485715652</v>
+        <v>58569.16012351852</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.2693512478649214</v>
+        <v>0.3566726023776798</v>
       </c>
       <c r="B72" t="n">
-        <v>5983</v>
+        <v>7800</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>27.49813949044645</v>
+        <v>48.26170020470562</v>
       </c>
       <c r="B73" t="n">
-        <v>2187</v>
+        <v>1468</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>54.72692773302798</v>
+        <v>96.16672780703357</v>
       </c>
       <c r="B74" t="n">
-        <v>876</v>
+        <v>404</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>81.95571597560951</v>
+        <v>144.0717554093615</v>
       </c>
       <c r="B75" t="n">
-        <v>390</v>
+        <v>170</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>109.184504218191</v>
+        <v>191.9767830116894</v>
       </c>
       <c r="B76" t="n">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136.4132924607726</v>
+        <v>239.8818106140174</v>
       </c>
       <c r="B77" t="n">
-        <v>113</v>
+        <v>40</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>163.6420807033541</v>
+        <v>287.7868382163453</v>
       </c>
       <c r="B78" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>190.8708689459357</v>
+        <v>335.6918658186733</v>
       </c>
       <c r="B79" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>218.0996571885172</v>
+        <v>383.5968934210012</v>
       </c>
       <c r="B80" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>245.3284454310987</v>
+        <v>431.5019210233291</v>
       </c>
       <c r="B81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>272.5572336736802</v>
+        <v>479.4069486256571</v>
       </c>
       <c r="B82" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>299.7860219162617</v>
+        <v>527.311976227985</v>
       </c>
       <c r="B83" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>327.0148101588433</v>
+        <v>575.2170038303129</v>
       </c>
       <c r="B84" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>354.2435984014248</v>
+        <v>623.1220314326409</v>
       </c>
       <c r="B85" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>381.4723866440063</v>
+        <v>671.0270590349688</v>
       </c>
       <c r="B86" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>408.7011748865879</v>
+        <v>718.9320866372968</v>
       </c>
       <c r="B87" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>435.9299631291694</v>
+        <v>766.8371142396247</v>
       </c>
       <c r="B88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>463.1587513717509</v>
+        <v>814.7421418419526</v>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>490.3875396143324</v>
+        <v>862.6471694442806</v>
       </c>
       <c r="B90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>517.616327856914</v>
+        <v>910.5521970466085</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>544.8451160994955</v>
+        <v>958.4572246489365</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>572.0739043420771</v>
+        <v>1006.362252251264</v>
       </c>
       <c r="B93" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>599.3026925846586</v>
+        <v>1054.267279853593</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>626.5314808272401</v>
+        <v>1102.17230745592</v>
       </c>
       <c r="B95" t="n">
         <v>1</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>653.7602690698217</v>
+        <v>1150.077335058248</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>680.9890573124032</v>
+        <v>1197.982362660576</v>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>708.2178455549847</v>
+        <v>1245.887390262904</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>735.4466337975663</v>
+        <v>1293.792417865232</v>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>762.6754220401479</v>
+        <v>1341.69744546756</v>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>789.9042102827293</v>
+        <v>1389.602473069888</v>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>817.1329985253109</v>
+        <v>1437.507500672216</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>844.3617867678923</v>
+        <v>1485.412528274544</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>871.5905750104739</v>
+        <v>1533.317555876872</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>898.8193632530555</v>
+        <v>1581.2225834792</v>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>926.0481514956369</v>
+        <v>1629.127611081528</v>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-4.879217183731744e+68</v>
+        <v>-2.414328715590312e+70</v>
       </c>
       <c r="B107" t="n">
         <v>1</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-4.739769615269744e+68</v>
+        <v>-2.345346862241633e+70</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-4.600322046807744e+68</v>
+        <v>-2.276365008892953e+70</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-4.460874478345743e+68</v>
+        <v>-2.207383155544274e+70</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-4.321426909883743e+68</v>
+        <v>-2.138401302195595e+70</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-4.181979341421743e+68</v>
+        <v>-2.069419448846916e+70</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-4.042531772959743e+68</v>
+        <v>-2.000437595498237e+70</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-3.903084204497743e+68</v>
+        <v>-1.931455742149558e+70</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-3.763636636035743e+68</v>
+        <v>-1.862473888800879e+70</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-3.624189067573742e+68</v>
+        <v>-1.7934920354522e+70</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-3.484741499111742e+68</v>
+        <v>-1.724510182103521e+70</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-3.345293930649742e+68</v>
+        <v>-1.655528328754842e+70</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-3.205846362187742e+68</v>
+        <v>-1.586546475406163e+70</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-3.066398793725742e+68</v>
+        <v>-1.517564622057484e+70</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-2.926951225263742e+68</v>
+        <v>-1.448582768708805e+70</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-2.787503656801742e+68</v>
+        <v>-1.379600915360126e+70</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-2.648056088339741e+68</v>
+        <v>-1.310619062011446e+70</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-2.508608519877741e+68</v>
+        <v>-1.241637208662767e+70</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-2.369160951415741e+68</v>
+        <v>-1.172655355314088e+70</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-2.229713382953741e+68</v>
+        <v>-1.103673501965409e+70</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-2.090265814491741e+68</v>
+        <v>-1.03469164861673e+70</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-1.95081824602974e+68</v>
+        <v>-9.657097952680511e+69</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-1.81137067756774e+68</v>
+        <v>-8.967279419193721e+69</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-1.67192310910574e+68</v>
+        <v>-8.277460885706931e+69</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-1.53247554064374e+68</v>
+        <v>-7.587642352220138e+69</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-1.39302797218174e+68</v>
+        <v>-6.897823818733348e+69</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-1.25358040371974e+68</v>
+        <v>-6.208005285246558e+69</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-1.11413283525774e+68</v>
+        <v>-5.518186751759765e+69</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-9.746852667957393e+67</v>
+        <v>-4.828368218272975e+69</v>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-8.352376983337393e+67</v>
+        <v>-4.138549684786185e+69</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-6.957901298717393e+67</v>
+        <v>-3.448731151299395e+69</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-5.563425614097389e+67</v>
+        <v>-2.758912617812602e+69</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>-4.168949929477389e+67</v>
+        <v>-2.069094084325812e+69</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>-2.774474244857389e+67</v>
+        <v>-1.379275550839023e+69</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>-1.379998560237389e+67</v>
+        <v>-6.894570173522296e+68</v>
       </c>
       <c r="B141" t="n">
         <v>9998</v>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14300.05046894063</v>
+        <v>9234.275227583579</v>
       </c>
       <c r="B2" t="n">
-        <v>2560</v>
+        <v>3474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117630.3460135587</v>
+        <v>143219.5987173916</v>
       </c>
       <c r="B3" t="n">
-        <v>3061</v>
+        <v>3144</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>220960.6415581767</v>
+        <v>277204.9222071996</v>
       </c>
       <c r="B4" t="n">
-        <v>1750</v>
+        <v>1609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>324290.9371027948</v>
+        <v>411190.2456970076</v>
       </c>
       <c r="B5" t="n">
-        <v>1040</v>
+        <v>819</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>427621.2326474128</v>
+        <v>545175.5691868156</v>
       </c>
       <c r="B6" t="n">
-        <v>605</v>
+        <v>383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>530951.5281920308</v>
+        <v>679160.8926766237</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>232</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>634281.8237366489</v>
+        <v>813146.2161664317</v>
       </c>
       <c r="B8" t="n">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>737612.1192812669</v>
+        <v>947131.5396562397</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>840942.414825885</v>
+        <v>1081116.863146048</v>
       </c>
       <c r="B10" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>944272.710370503</v>
+        <v>1215102.186635856</v>
       </c>
       <c r="B11" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1047603.005915121</v>
+        <v>1349087.510125664</v>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1150933.301459739</v>
+        <v>1483072.833615472</v>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1254263.597004357</v>
+        <v>1617058.15710528</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1357593.892548975</v>
+        <v>1751043.480595088</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1460924.188093593</v>
+        <v>1885028.804084896</v>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1564254.483638211</v>
+        <v>2019014.127574704</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1667584.779182829</v>
+        <v>2152999.451064512</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1770915.074727447</v>
+        <v>2286984.77455432</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1874245.370272065</v>
+        <v>2420970.098044128</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1977575.665816683</v>
+        <v>2554955.421533936</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2080905.961361301</v>
+        <v>2688940.745023744</v>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2184236.256905919</v>
+        <v>2822926.068513552</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2287566.552450538</v>
+        <v>2956911.39200336</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2390896.847995156</v>
+        <v>3090896.715493168</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2494227.143539774</v>
+        <v>3224882.038982976</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2597557.439084392</v>
+        <v>3358867.362472784</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2700887.73462901</v>
+        <v>3492852.685962592</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2804218.030173628</v>
+        <v>3626838.0094524</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2907548.325718246</v>
+        <v>3760823.332942208</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,10 +824,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3010878.621262864</v>
+        <v>3894808.656432016</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3114208.916807482</v>
+        <v>4028793.979921824</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3217539.2123521</v>
+        <v>4162779.303411632</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3320869.507896718</v>
+        <v>4296764.62690144</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3424199.803441336</v>
+        <v>4430749.950391248</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3527530.098985954</v>
+        <v>4564735.273881056</v>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>186.6936451040915</v>
+        <v>200.5162618683445</v>
       </c>
       <c r="B37" t="n">
-        <v>1520</v>
+        <v>1743</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1903.825012116281</v>
+        <v>2030.864059235412</v>
       </c>
       <c r="B38" t="n">
-        <v>2838</v>
+        <v>2937</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3620.95637912847</v>
+        <v>3861.21185660248</v>
       </c>
       <c r="B39" t="n">
-        <v>2007</v>
+        <v>2040</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5338.08774614066</v>
+        <v>5691.559653969547</v>
       </c>
       <c r="B40" t="n">
-        <v>1284</v>
+        <v>1242</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7055.219113152849</v>
+        <v>7521.907451336615</v>
       </c>
       <c r="B41" t="n">
-        <v>781</v>
+        <v>733</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8772.350480165038</v>
+        <v>9352.255248703683</v>
       </c>
       <c r="B42" t="n">
-        <v>546</v>
+        <v>427</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>10489.48184717723</v>
+        <v>11182.60304607075</v>
       </c>
       <c r="B43" t="n">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>12206.61321418942</v>
+        <v>13012.95084343782</v>
       </c>
       <c r="B44" t="n">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>13923.7445812016</v>
+        <v>14843.29864080489</v>
       </c>
       <c r="B45" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15640.87594821379</v>
+        <v>16673.64643817196</v>
       </c>
       <c r="B46" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>17358.00731522599</v>
+        <v>18503.99423553902</v>
       </c>
       <c r="B47" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>19075.13868223818</v>
+        <v>20334.34203290609</v>
       </c>
       <c r="B48" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>20792.27004925036</v>
+        <v>22164.68983027316</v>
       </c>
       <c r="B49" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>22509.40141626255</v>
+        <v>23995.03762764022</v>
       </c>
       <c r="B50" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>24226.53278327474</v>
+        <v>25825.38542500729</v>
       </c>
       <c r="B51" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>25943.66415028693</v>
+        <v>27655.73322237436</v>
       </c>
       <c r="B52" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>27660.79551729912</v>
+        <v>29486.08101974143</v>
       </c>
       <c r="B53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>29377.92688431131</v>
+        <v>31316.4288171085</v>
       </c>
       <c r="B54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>31095.0582513235</v>
+        <v>33146.77661447557</v>
       </c>
       <c r="B55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>32812.18961833569</v>
+        <v>34977.12441184263</v>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>34529.32098534788</v>
+        <v>36807.4722092097</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>36246.45235236007</v>
+        <v>38637.82000657677</v>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>37963.58371937225</v>
+        <v>40468.16780394383</v>
       </c>
       <c r="B59" t="n">
         <v>2</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>39680.71508638444</v>
+        <v>42298.5156013109</v>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>41397.84645339663</v>
+        <v>44128.86339867797</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>43114.97782040882</v>
+        <v>45959.21119604503</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>44832.10918742101</v>
+        <v>47789.5589934121</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>46549.2405544332</v>
+        <v>49619.90679077918</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>48266.37192144539</v>
+        <v>51450.25458814624</v>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>49983.50328845758</v>
+        <v>53280.60238551331</v>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>51700.63465546977</v>
+        <v>55110.95018288038</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>53417.76602248196</v>
+        <v>56941.29798024744</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>55134.89738949414</v>
+        <v>58771.64577761451</v>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>56852.02875650633</v>
+        <v>60601.99357498158</v>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>58569.16012351852</v>
+        <v>62432.34137234864</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.3566726023776798</v>
+        <v>0.3867702630303068</v>
       </c>
       <c r="B72" t="n">
-        <v>7800</v>
+        <v>6617</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>48.26170020470562</v>
+        <v>32.44388810698388</v>
       </c>
       <c r="B73" t="n">
-        <v>1468</v>
+        <v>1957</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>96.16672780703357</v>
+        <v>64.50100595093744</v>
       </c>
       <c r="B74" t="n">
-        <v>404</v>
+        <v>704</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>144.0717554093615</v>
+        <v>96.55812379489102</v>
       </c>
       <c r="B75" t="n">
-        <v>170</v>
+        <v>328</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>191.9767830116894</v>
+        <v>128.6152416388446</v>
       </c>
       <c r="B76" t="n">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>239.8818106140174</v>
+        <v>160.6723594827982</v>
       </c>
       <c r="B77" t="n">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>287.7868382163453</v>
+        <v>192.7294773267517</v>
       </c>
       <c r="B78" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>335.6918658186733</v>
+        <v>224.7865951707053</v>
       </c>
       <c r="B79" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>383.5968934210012</v>
+        <v>256.8437130146589</v>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>431.5019210233291</v>
+        <v>288.9008308586124</v>
       </c>
       <c r="B81" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>479.4069486256571</v>
+        <v>320.957948702566</v>
       </c>
       <c r="B82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>527.311976227985</v>
+        <v>353.0150665465196</v>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>575.2170038303129</v>
+        <v>385.0721843904732</v>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>623.1220314326409</v>
+        <v>417.1293022344267</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>671.0270590349688</v>
+        <v>449.1864200783803</v>
       </c>
       <c r="B86" t="n">
         <v>1</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>718.9320866372968</v>
+        <v>481.2435379223339</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>766.8371142396247</v>
+        <v>513.3006557662874</v>
       </c>
       <c r="B88" t="n">
         <v>0</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>814.7421418419526</v>
+        <v>545.357773610241</v>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>862.6471694442806</v>
+        <v>577.4148914541945</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>910.5521970466085</v>
+        <v>609.4720092981481</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>958.4572246489365</v>
+        <v>641.5291271421016</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1006.362252251264</v>
+        <v>673.5862449860552</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1054.267279853593</v>
+        <v>705.6433628300088</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1102.17230745592</v>
+        <v>737.7004806739624</v>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1150.077335058248</v>
+        <v>769.757598517916</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1197.982362660576</v>
+        <v>801.8147163618695</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1245.887390262904</v>
+        <v>833.8718342058231</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1293.792417865232</v>
+        <v>865.9289520497766</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1341.69744546756</v>
+        <v>897.9860698937302</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1389.602473069888</v>
+        <v>930.0431877376838</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1437.507500672216</v>
+        <v>962.1003055816374</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1485.412528274544</v>
+        <v>994.1574234255909</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1533.317555876872</v>
+        <v>1026.214541269544</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1581.2225834792</v>
+        <v>1058.271659113498</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1629.127611081528</v>
+        <v>1090.328776957452</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-2.414328715590312e+70</v>
+        <v>-7.932261775455884e+65</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-2.345346862241633e+70</v>
+        <v>9.232540814522995e+66</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-2.276365008892953e+70</v>
+        <v>1.925830780659158e+67</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-2.207383155544274e+70</v>
+        <v>2.928407479866016e+67</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-2.138401302195595e+70</v>
+        <v>3.930984179072875e+67</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-2.069419448846916e+70</v>
+        <v>4.933560878279733e+67</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-2.000437595498237e+70</v>
+        <v>5.936137577486591e+67</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-1.931455742149558e+70</v>
+        <v>6.938714276693449e+67</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-1.862473888800879e+70</v>
+        <v>7.941290975900308e+67</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-1.7934920354522e+70</v>
+        <v>8.943867675107166e+67</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-1.724510182103521e+70</v>
+        <v>9.946444374314025e+67</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-1.655528328754842e+70</v>
+        <v>1.094902107352088e+68</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-1.586546475406163e+70</v>
+        <v>1.195159777272774e+68</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-1.517564622057484e+70</v>
+        <v>1.29541744719346e+68</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-1.448582768708805e+70</v>
+        <v>1.395675117114146e+68</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-1.379600915360126e+70</v>
+        <v>1.495932787034832e+68</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-1.310619062011446e+70</v>
+        <v>1.596190456955518e+68</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-1.241637208662767e+70</v>
+        <v>1.696448126876203e+68</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-1.172655355314088e+70</v>
+        <v>1.796705796796889e+68</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-1.103673501965409e+70</v>
+        <v>1.896963466717575e+68</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-1.03469164861673e+70</v>
+        <v>1.997221136638261e+68</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-9.657097952680511e+69</v>
+        <v>2.097478806558947e+68</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-8.967279419193721e+69</v>
+        <v>2.197736476479633e+68</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-8.277460885706931e+69</v>
+        <v>2.297994146400318e+68</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-7.587642352220138e+69</v>
+        <v>2.398251816321004e+68</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-6.897823818733348e+69</v>
+        <v>2.49850948624169e+68</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-6.208005285246558e+69</v>
+        <v>2.598767156162376e+68</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-5.518186751759765e+69</v>
+        <v>2.699024826083062e+68</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-4.828368218272975e+69</v>
+        <v>2.799282496003748e+68</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-4.138549684786185e+69</v>
+        <v>2.899540165924433e+68</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-3.448731151299395e+69</v>
+        <v>2.999797835845119e+68</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-2.758912617812602e+69</v>
+        <v>3.100055505765805e+68</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>-2.069094084325812e+69</v>
+        <v>3.200313175686491e+68</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>-1.379275550839023e+69</v>
+        <v>3.300570845607177e+68</v>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>-6.894570173522296e+68</v>
+        <v>3.400828515527862e+68</v>
       </c>
       <c r="B141" t="n">
-        <v>9998</v>
+        <v>1</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9234.275227583579</v>
+        <v>9793.61336310492</v>
       </c>
       <c r="B2" t="n">
-        <v>3474</v>
+        <v>2487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>143219.5987173916</v>
+        <v>115326.8710773276</v>
       </c>
       <c r="B3" t="n">
-        <v>3144</v>
+        <v>3111</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>277204.9222071996</v>
+        <v>220860.1287915503</v>
       </c>
       <c r="B4" t="n">
-        <v>1609</v>
+        <v>1832</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>411190.2456970076</v>
+        <v>326393.386505773</v>
       </c>
       <c r="B5" t="n">
-        <v>819</v>
+        <v>1040</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>545175.5691868156</v>
+        <v>431926.6442199957</v>
       </c>
       <c r="B6" t="n">
-        <v>383</v>
+        <v>547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>679160.8926766237</v>
+        <v>537459.9019342184</v>
       </c>
       <c r="B7" t="n">
-        <v>232</v>
+        <v>344</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>813146.2161664317</v>
+        <v>642993.159648441</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>225</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>947131.5396562397</v>
+        <v>748526.4173626638</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1081116.863146048</v>
+        <v>854059.6750768864</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1215102.186635856</v>
+        <v>959592.9327911091</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1349087.510125664</v>
+        <v>1065126.190505332</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1483072.833615472</v>
+        <v>1170659.448219554</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1617058.15710528</v>
+        <v>1276192.705933777</v>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1751043.480595088</v>
+        <v>1381725.963648</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1885028.804084896</v>
+        <v>1487259.221362223</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2019014.127574704</v>
+        <v>1592792.479076445</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2152999.451064512</v>
+        <v>1698325.736790668</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2286984.77455432</v>
+        <v>1803858.994504891</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2420970.098044128</v>
+        <v>1909392.252219113</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2554955.421533936</v>
+        <v>2014925.509933336</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2688940.745023744</v>
+        <v>2120458.767647559</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2822926.068513552</v>
+        <v>2225992.025361781</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2956911.39200336</v>
+        <v>2331525.283076004</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3090896.715493168</v>
+        <v>2437058.540790227</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3224882.038982976</v>
+        <v>2542591.798504449</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3358867.362472784</v>
+        <v>2648125.056218672</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3492852.685962592</v>
+        <v>2753658.313932895</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3626838.0094524</v>
+        <v>2859191.571647118</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3760823.332942208</v>
+        <v>2964724.82936134</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,10 +824,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3894808.656432016</v>
+        <v>3070258.087075563</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4028793.979921824</v>
+        <v>3175791.344789786</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,10 +850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4162779.303411632</v>
+        <v>3281324.602504008</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4296764.62690144</v>
+        <v>3386857.860218231</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4430749.950391248</v>
+        <v>3492391.117932454</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4564735.273881056</v>
+        <v>3597924.375646676</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>200.5162618683445</v>
+        <v>227.8615884013128</v>
       </c>
       <c r="B37" t="n">
-        <v>1743</v>
+        <v>1348</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2030.864059235412</v>
+        <v>1797.467426524355</v>
       </c>
       <c r="B38" t="n">
-        <v>2937</v>
+        <v>2665</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3861.21185660248</v>
+        <v>3367.073264647397</v>
       </c>
       <c r="B39" t="n">
-        <v>2040</v>
+        <v>2074</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5691.559653969547</v>
+        <v>4936.679102770438</v>
       </c>
       <c r="B40" t="n">
-        <v>1242</v>
+        <v>1366</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7521.907451336615</v>
+        <v>6506.28494089348</v>
       </c>
       <c r="B41" t="n">
-        <v>733</v>
+        <v>827</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9352.255248703683</v>
+        <v>8075.890779016521</v>
       </c>
       <c r="B42" t="n">
-        <v>427</v>
+        <v>554</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11182.60304607075</v>
+        <v>9645.496617139564</v>
       </c>
       <c r="B43" t="n">
-        <v>289</v>
+        <v>383</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>13012.95084343782</v>
+        <v>11215.10245526261</v>
       </c>
       <c r="B44" t="n">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14843.29864080489</v>
+        <v>12784.70829338565</v>
       </c>
       <c r="B45" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>16673.64643817196</v>
+        <v>14354.31413150869</v>
       </c>
       <c r="B46" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>18503.99423553902</v>
+        <v>15923.91996963173</v>
       </c>
       <c r="B47" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>20334.34203290609</v>
+        <v>17493.52580775477</v>
       </c>
       <c r="B48" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>22164.68983027316</v>
+        <v>19063.13164587782</v>
       </c>
       <c r="B49" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>23995.03762764022</v>
+        <v>20632.73748400086</v>
       </c>
       <c r="B50" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>25825.38542500729</v>
+        <v>22202.3433221239</v>
       </c>
       <c r="B51" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>27655.73322237436</v>
+        <v>23771.94916024694</v>
       </c>
       <c r="B52" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>29486.08101974143</v>
+        <v>25341.55499836998</v>
       </c>
       <c r="B53" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>31316.4288171085</v>
+        <v>26911.16083649303</v>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>33146.77661447557</v>
+        <v>28480.76667461606</v>
       </c>
       <c r="B55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>34977.12441184263</v>
+        <v>30050.37251273911</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>36807.4722092097</v>
+        <v>31619.97835086215</v>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>38637.82000657677</v>
+        <v>33189.58418898519</v>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>40468.16780394383</v>
+        <v>34759.19002710823</v>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>42298.5156013109</v>
+        <v>36328.79586523127</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>44128.86339867797</v>
+        <v>37898.40170335432</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>45959.21119604503</v>
+        <v>39468.00754147736</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>47789.5589934121</v>
+        <v>41037.6133796004</v>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>49619.90679077918</v>
+        <v>42607.21921772344</v>
       </c>
       <c r="B64" t="n">
         <v>0</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>51450.25458814624</v>
+        <v>44176.82505584649</v>
       </c>
       <c r="B65" t="n">
         <v>1</v>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>53280.60238551331</v>
+        <v>45746.43089396953</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>55110.95018288038</v>
+        <v>47316.03673209257</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>56941.29798024744</v>
+        <v>48885.64257021561</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>58771.64577761451</v>
+        <v>50455.24840833865</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>60601.99357498158</v>
+        <v>52024.85424646169</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>62432.34137234864</v>
+        <v>53594.46008458474</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.3867702630303068</v>
+        <v>0.2080488252645446</v>
       </c>
       <c r="B72" t="n">
-        <v>6617</v>
+        <v>7514</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>32.44388810698388</v>
+        <v>43.88294616666068</v>
       </c>
       <c r="B73" t="n">
-        <v>1957</v>
+        <v>1528</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>64.50100595093744</v>
+        <v>87.55784350805681</v>
       </c>
       <c r="B74" t="n">
-        <v>704</v>
+        <v>508</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>96.55812379489102</v>
+        <v>131.2327408494529</v>
       </c>
       <c r="B75" t="n">
-        <v>328</v>
+        <v>211</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128.6152416388446</v>
+        <v>174.9076381908491</v>
       </c>
       <c r="B76" t="n">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>160.6723594827982</v>
+        <v>218.5825355322452</v>
       </c>
       <c r="B77" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>192.7294773267517</v>
+        <v>262.2574328736413</v>
       </c>
       <c r="B78" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>224.7865951707053</v>
+        <v>305.9323302150375</v>
       </c>
       <c r="B79" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>256.8437130146589</v>
+        <v>349.6072275564336</v>
       </c>
       <c r="B80" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>288.9008308586124</v>
+        <v>393.2821248978297</v>
       </c>
       <c r="B81" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>320.957948702566</v>
+        <v>436.9570222392259</v>
       </c>
       <c r="B82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>353.0150665465196</v>
+        <v>480.631919580622</v>
       </c>
       <c r="B83" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>385.0721843904732</v>
+        <v>524.3068169220181</v>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>417.1293022344267</v>
+        <v>567.9817142634142</v>
       </c>
       <c r="B85" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>449.1864200783803</v>
+        <v>611.6566116048105</v>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>481.2435379223339</v>
+        <v>655.3315089462066</v>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>513.3006557662874</v>
+        <v>699.0064062876027</v>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>545.357773610241</v>
+        <v>742.6813036289988</v>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>577.4148914541945</v>
+        <v>786.3562009703949</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>609.4720092981481</v>
+        <v>830.0310983117911</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>641.5291271421016</v>
+        <v>873.7059956531872</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>673.5862449860552</v>
+        <v>917.3808929945833</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>705.6433628300088</v>
+        <v>961.0557903359795</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>737.7004806739624</v>
+        <v>1004.730687677376</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>769.757598517916</v>
+        <v>1048.405585018772</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>801.8147163618695</v>
+        <v>1092.080482360168</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>833.8718342058231</v>
+        <v>1135.755379701564</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>865.9289520497766</v>
+        <v>1179.43027704296</v>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>897.9860698937302</v>
+        <v>1223.105174384356</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>930.0431877376838</v>
+        <v>1266.780071725752</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>962.1003055816374</v>
+        <v>1310.454969067149</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>994.1574234255909</v>
+        <v>1354.129866408545</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1026.214541269544</v>
+        <v>1397.804763749941</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1058.271659113498</v>
+        <v>1441.479661091337</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1090.328776957452</v>
+        <v>1485.154558432733</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-7.932261775455884e+65</v>
+        <v>-4.558483893154849e+69</v>
       </c>
       <c r="B107" t="n">
         <v>9999</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>9.232540814522995e+66</v>
+        <v>1.506260509884637e+69</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1.925830780659158e+67</v>
+        <v>7.571004912924123e+69</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2.928407479866016e+67</v>
+        <v>1.363574931596361e+70</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>3.930984179072875e+67</v>
+        <v>1.970049371900309e+70</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>4.933560878279733e+67</v>
+        <v>2.576523812204258e+70</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>5.936137577486591e+67</v>
+        <v>3.182998252508207e+70</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>6.938714276693449e+67</v>
+        <v>3.789472692812155e+70</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>7.941290975900308e+67</v>
+        <v>4.395947133116104e+70</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>8.943867675107166e+67</v>
+        <v>5.002421573420052e+70</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>9.946444374314025e+67</v>
+        <v>5.608896013724001e+70</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1.094902107352088e+68</v>
+        <v>6.21537045402795e+70</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1.195159777272774e+68</v>
+        <v>6.821844894331898e+70</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1.29541744719346e+68</v>
+        <v>7.428319334635846e+70</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1.395675117114146e+68</v>
+        <v>8.034793774939795e+70</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1.495932787034832e+68</v>
+        <v>8.641268215243744e+70</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1.596190456955518e+68</v>
+        <v>9.247742655547692e+70</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1.696448126876203e+68</v>
+        <v>9.85421709585164e+70</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1.796705796796889e+68</v>
+        <v>1.046069153615559e+71</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1.896963466717575e+68</v>
+        <v>1.106716597645954e+71</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1.997221136638261e+68</v>
+        <v>1.167364041676349e+71</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2.097478806558947e+68</v>
+        <v>1.228011485706743e+71</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2.197736476479633e+68</v>
+        <v>1.288658929737138e+71</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2.297994146400318e+68</v>
+        <v>1.349306373767533e+71</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2.398251816321004e+68</v>
+        <v>1.409953817797928e+71</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2.49850948624169e+68</v>
+        <v>1.470601261828323e+71</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2.598767156162376e+68</v>
+        <v>1.531248705858718e+71</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2.699024826083062e+68</v>
+        <v>1.591896149889113e+71</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2.799282496003748e+68</v>
+        <v>1.652543593919507e+71</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2.899540165924433e+68</v>
+        <v>1.713191037949902e+71</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2.999797835845119e+68</v>
+        <v>1.773838481980297e+71</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>3.100055505765805e+68</v>
+        <v>1.834485926010692e+71</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>3.200313175686491e+68</v>
+        <v>1.895133370041087e+71</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>3.300570845607177e+68</v>
+        <v>1.955780814071482e+71</v>
       </c>
       <c r="B140" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>3.400828515527862e+68</v>
+        <v>2.016428258101876e+71</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9793.61336310492</v>
+        <v>6050.825907019175</v>
       </c>
       <c r="B2" t="n">
-        <v>2487</v>
+        <v>1825</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115326.8710773276</v>
+        <v>97912.10634031559</v>
       </c>
       <c r="B3" t="n">
-        <v>3111</v>
+        <v>2898</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>220860.1287915503</v>
+        <v>189773.386773612</v>
       </c>
       <c r="B4" t="n">
-        <v>1832</v>
+        <v>1978</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>326393.386505773</v>
+        <v>281634.6672069085</v>
       </c>
       <c r="B5" t="n">
-        <v>1040</v>
+        <v>1172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>431926.6442199957</v>
+        <v>373495.9476402049</v>
       </c>
       <c r="B6" t="n">
-        <v>547</v>
+        <v>741</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>537459.9019342184</v>
+        <v>465357.2280735013</v>
       </c>
       <c r="B7" t="n">
-        <v>344</v>
+        <v>433</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>642993.159648441</v>
+        <v>557218.5085067977</v>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>748526.4173626638</v>
+        <v>649079.7889400941</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>198</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>854059.6750768864</v>
+        <v>740941.0693733905</v>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>959592.9327911091</v>
+        <v>832802.349806687</v>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1065126.190505332</v>
+        <v>924663.6302399833</v>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1170659.448219554</v>
+        <v>1016524.91067328</v>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1276192.705933777</v>
+        <v>1108386.191106576</v>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1381725.963648</v>
+        <v>1200247.471539873</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1487259.221362223</v>
+        <v>1292108.751973169</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1592792.479076445</v>
+        <v>1383970.032406465</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1698325.736790668</v>
+        <v>1475831.312839762</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1803858.994504891</v>
+        <v>1567692.593273058</v>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1909392.252219113</v>
+        <v>1659553.873706355</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2014925.509933336</v>
+        <v>1751415.154139651</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2120458.767647559</v>
+        <v>1843276.434572947</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2225992.025361781</v>
+        <v>1935137.715006244</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2331525.283076004</v>
+        <v>2026998.99543954</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2437058.540790227</v>
+        <v>2118860.275872836</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2542591.798504449</v>
+        <v>2210721.556306133</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2648125.056218672</v>
+        <v>2302582.836739429</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2753658.313932895</v>
+        <v>2394444.117172726</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2859191.571647118</v>
+        <v>2486305.397606022</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2964724.82936134</v>
+        <v>2578166.678039318</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,10 +824,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3070258.087075563</v>
+        <v>2670027.958472615</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3175791.344789786</v>
+        <v>2761889.238905911</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,10 +850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3281324.602504008</v>
+        <v>2853750.519339208</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3386857.860218231</v>
+        <v>2945611.799772504</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3492391.117932454</v>
+        <v>3037473.0802058</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3597924.375646676</v>
+        <v>3129334.360639097</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>227.8615884013128</v>
+        <v>297.5151619680543</v>
       </c>
       <c r="B37" t="n">
-        <v>1348</v>
+        <v>1585</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1797.467426524355</v>
+        <v>1964.016054352688</v>
       </c>
       <c r="B38" t="n">
-        <v>2665</v>
+        <v>2773</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3367.073264647397</v>
+        <v>3630.516946737322</v>
       </c>
       <c r="B39" t="n">
-        <v>2074</v>
+        <v>1970</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4936.679102770438</v>
+        <v>5297.017839121956</v>
       </c>
       <c r="B40" t="n">
-        <v>1366</v>
+        <v>1315</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6506.28494089348</v>
+        <v>6963.51873150659</v>
       </c>
       <c r="B41" t="n">
-        <v>827</v>
+        <v>764</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8075.890779016521</v>
+        <v>8630.019623891223</v>
       </c>
       <c r="B42" t="n">
-        <v>554</v>
+        <v>527</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9645.496617139564</v>
+        <v>10296.52051627586</v>
       </c>
       <c r="B43" t="n">
-        <v>383</v>
+        <v>307</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>11215.10245526261</v>
+        <v>11963.02140866049</v>
       </c>
       <c r="B44" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>12784.70829338565</v>
+        <v>13629.52230104512</v>
       </c>
       <c r="B45" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>14354.31413150869</v>
+        <v>15296.02319342976</v>
       </c>
       <c r="B46" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>15923.91996963173</v>
+        <v>16962.52408581439</v>
       </c>
       <c r="B47" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17493.52580775477</v>
+        <v>18629.02497819902</v>
       </c>
       <c r="B48" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>19063.13164587782</v>
+        <v>20295.52587058366</v>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20632.73748400086</v>
+        <v>21962.02676296829</v>
       </c>
       <c r="B50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>22202.3433221239</v>
+        <v>23628.52765535293</v>
       </c>
       <c r="B51" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>23771.94916024694</v>
+        <v>25295.02854773756</v>
       </c>
       <c r="B52" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>25341.55499836998</v>
+        <v>26961.52944012219</v>
       </c>
       <c r="B53" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>26911.16083649303</v>
+        <v>28628.03033250683</v>
       </c>
       <c r="B54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>28480.76667461606</v>
+        <v>30294.53122489146</v>
       </c>
       <c r="B55" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>30050.37251273911</v>
+        <v>31961.0321172761</v>
       </c>
       <c r="B56" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>31619.97835086215</v>
+        <v>33627.53300966073</v>
       </c>
       <c r="B57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>33189.58418898519</v>
+        <v>35294.03390204536</v>
       </c>
       <c r="B58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>34759.19002710823</v>
+        <v>36960.53479442999</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>36328.79586523127</v>
+        <v>38627.03568681463</v>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>37898.40170335432</v>
+        <v>40293.53657919927</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>39468.00754147736</v>
+        <v>41960.0374715839</v>
       </c>
       <c r="B62" t="n">
         <v>1</v>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>41037.6133796004</v>
+        <v>43626.53836396853</v>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>42607.21921772344</v>
+        <v>45293.03925635316</v>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>44176.82505584649</v>
+        <v>46959.5401487378</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>45746.43089396953</v>
+        <v>48626.04104112244</v>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>47316.03673209257</v>
+        <v>50292.54193350707</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>48885.64257021561</v>
+        <v>51959.0428258917</v>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>50455.24840833865</v>
+        <v>53625.54371827633</v>
       </c>
       <c r="B69" t="n">
         <v>1</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>52024.85424646169</v>
+        <v>55292.04461066097</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>53594.46008458474</v>
+        <v>56958.5455030456</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.2080488252645446</v>
+        <v>0.3228204131684999</v>
       </c>
       <c r="B72" t="n">
-        <v>7514</v>
+        <v>7038</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>43.88294616666068</v>
+        <v>37.35545444265147</v>
       </c>
       <c r="B73" t="n">
-        <v>1528</v>
+        <v>1794</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>87.55784350805681</v>
+        <v>74.38808847213444</v>
       </c>
       <c r="B74" t="n">
-        <v>508</v>
+        <v>610</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131.2327408494529</v>
+        <v>111.4207225016174</v>
       </c>
       <c r="B75" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>174.9076381908491</v>
+        <v>148.4533565311004</v>
       </c>
       <c r="B76" t="n">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>218.5825355322452</v>
+        <v>185.4859905605834</v>
       </c>
       <c r="B77" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>262.2574328736413</v>
+        <v>222.5186245900663</v>
       </c>
       <c r="B78" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>305.9323302150375</v>
+        <v>259.5512586195493</v>
       </c>
       <c r="B79" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>349.6072275564336</v>
+        <v>296.5838926490322</v>
       </c>
       <c r="B80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>393.2821248978297</v>
+        <v>333.6165266785152</v>
       </c>
       <c r="B81" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>436.9570222392259</v>
+        <v>370.6491607079982</v>
       </c>
       <c r="B82" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>480.631919580622</v>
+        <v>407.6817947374811</v>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>524.3068169220181</v>
+        <v>444.7144287669641</v>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>567.9817142634142</v>
+        <v>481.7470627964471</v>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>611.6566116048105</v>
+        <v>518.7796968259302</v>
       </c>
       <c r="B86" t="n">
         <v>2</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>655.3315089462066</v>
+        <v>555.8123308554131</v>
       </c>
       <c r="B87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>699.0064062876027</v>
+        <v>592.8449648848961</v>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>742.6813036289988</v>
+        <v>629.8775989143791</v>
       </c>
       <c r="B89" t="n">
         <v>1</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>786.3562009703949</v>
+        <v>666.910232943862</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>830.0310983117911</v>
+        <v>703.942866973345</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>873.7059956531872</v>
+        <v>740.975501002828</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>917.3808929945833</v>
+        <v>778.0081350323109</v>
       </c>
       <c r="B93" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>961.0557903359795</v>
+        <v>815.0407690617939</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1004.730687677376</v>
+        <v>852.0734030912769</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1048.405585018772</v>
+        <v>889.1060371207598</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1092.080482360168</v>
+        <v>926.1386711502428</v>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1135.755379701564</v>
+        <v>963.1713051797258</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1179.43027704296</v>
+        <v>1000.203939209209</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1223.105174384356</v>
+        <v>1037.236573238692</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1266.780071725752</v>
+        <v>1074.269207268175</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1310.454969067149</v>
+        <v>1111.301841297658</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1354.129866408545</v>
+        <v>1148.334475327141</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1397.804763749941</v>
+        <v>1185.367109356624</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1441.479661091337</v>
+        <v>1222.399743386107</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1485.154558432733</v>
+        <v>1259.43237741559</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-4.558483893154849e+69</v>
+        <v>-3.260250812209071e+66</v>
       </c>
       <c r="B107" t="n">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1.506260509884637e+69</v>
+        <v>-3.166408640787946e+66</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>7.571004912924123e+69</v>
+        <v>-3.072566469366821e+66</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1.363574931596361e+70</v>
+        <v>-2.978724297945696e+66</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1.970049371900309e+70</v>
+        <v>-2.884882126524571e+66</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2.576523812204258e+70</v>
+        <v>-2.791039955103446e+66</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>3.182998252508207e+70</v>
+        <v>-2.697197783682321e+66</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>3.789472692812155e+70</v>
+        <v>-2.603355612261196e+66</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>4.395947133116104e+70</v>
+        <v>-2.509513440840071e+66</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>5.002421573420052e+70</v>
+        <v>-2.415671269418946e+66</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>5.608896013724001e+70</v>
+        <v>-2.321829097997822e+66</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>6.21537045402795e+70</v>
+        <v>-2.227986926576696e+66</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>6.821844894331898e+70</v>
+        <v>-2.134144755155572e+66</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>7.428319334635846e+70</v>
+        <v>-2.040302583734447e+66</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>8.034793774939795e+70</v>
+        <v>-1.946460412313322e+66</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>8.641268215243744e+70</v>
+        <v>-1.852618240892197e+66</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>9.247742655547692e+70</v>
+        <v>-1.758776069471072e+66</v>
       </c>
       <c r="B123" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>9.85421709585164e+70</v>
+        <v>-1.664933898049947e+66</v>
       </c>
       <c r="B124" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1.046069153615559e+71</v>
+        <v>-1.571091726628822e+66</v>
       </c>
       <c r="B125" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1.106716597645954e+71</v>
+        <v>-1.477249555207697e+66</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1.167364041676349e+71</v>
+        <v>-1.383407383786572e+66</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1.228011485706743e+71</v>
+        <v>-1.289565212365447e+66</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1.288658929737138e+71</v>
+        <v>-1.195723040944322e+66</v>
       </c>
       <c r="B129" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1.349306373767533e+71</v>
+        <v>-1.101880869523197e+66</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1.409953817797928e+71</v>
+        <v>-1.008038698102072e+66</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1.470601261828323e+71</v>
+        <v>-9.141965266809472e+65</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1.531248705858718e+71</v>
+        <v>-8.203543552598223e+65</v>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1.591896149889113e+71</v>
+        <v>-7.265121838386974e+65</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1.652543593919507e+71</v>
+        <v>-6.326700124175725e+65</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1.713191037949902e+71</v>
+        <v>-5.388278409964472e+65</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1.773838481980297e+71</v>
+        <v>-4.449856695753223e+65</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1.834485926010692e+71</v>
+        <v>-3.511434981541975e+65</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1.895133370041087e+71</v>
+        <v>-2.573013267330726e+65</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1.955780814071482e+71</v>
+        <v>-1.634591553119477e+65</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2.016428258101876e+71</v>
+        <v>-6.961698389082278e+64</v>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>9997</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6050.825907019175</v>
+        <v>12266.88818276355</v>
       </c>
       <c r="B2" t="n">
-        <v>1825</v>
+        <v>2163</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97912.10634031559</v>
+        <v>104650.4461261408</v>
       </c>
       <c r="B3" t="n">
-        <v>2898</v>
+        <v>2888</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>189773.386773612</v>
+        <v>197034.004069518</v>
       </c>
       <c r="B4" t="n">
-        <v>1978</v>
+        <v>1884</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>281634.6672069085</v>
+        <v>289417.5620128953</v>
       </c>
       <c r="B5" t="n">
-        <v>1172</v>
+        <v>1104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>373495.9476402049</v>
+        <v>381801.1199562725</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>465357.2280735013</v>
+        <v>474184.6778996498</v>
       </c>
       <c r="B7" t="n">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>557218.5085067977</v>
+        <v>566568.2358430271</v>
       </c>
       <c r="B8" t="n">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>649079.7889400941</v>
+        <v>658951.7937864043</v>
       </c>
       <c r="B9" t="n">
-        <v>198</v>
+        <v>148</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>740941.0693733905</v>
+        <v>751335.3517297816</v>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>832802.349806687</v>
+        <v>843718.9096731589</v>
       </c>
       <c r="B11" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>924663.6302399833</v>
+        <v>936102.4676165361</v>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1016524.91067328</v>
+        <v>1028486.025559913</v>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1108386.191106576</v>
+        <v>1120869.583503291</v>
       </c>
       <c r="B14" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1200247.471539873</v>
+        <v>1213253.141446668</v>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1292108.751973169</v>
+        <v>1305636.699390045</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1383970.032406465</v>
+        <v>1398020.257333422</v>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1475831.312839762</v>
+        <v>1490403.815276799</v>
       </c>
       <c r="B18" t="n">
         <v>10</v>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1567692.593273058</v>
+        <v>1582787.373220177</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1659553.873706355</v>
+        <v>1675170.931163554</v>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1751415.154139651</v>
+        <v>1767554.489106931</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1843276.434572947</v>
+        <v>1859938.047050308</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1935137.715006244</v>
+        <v>1952321.604993686</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2026998.99543954</v>
+        <v>2044705.162937063</v>
       </c>
       <c r="B24" t="n">
         <v>3</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2118860.275872836</v>
+        <v>2137088.72088044</v>
       </c>
       <c r="B25" t="n">
         <v>2</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2210721.556306133</v>
+        <v>2229472.278823818</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2302582.836739429</v>
+        <v>2321855.836767195</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2394444.117172726</v>
+        <v>2414239.394710572</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2486305.397606022</v>
+        <v>2506622.952653949</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2578166.678039318</v>
+        <v>2599006.510597326</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,10 +824,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2670027.958472615</v>
+        <v>2691390.068540704</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2761889.238905911</v>
+        <v>2783773.626484081</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2853750.519339208</v>
+        <v>2876157.184427458</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2945611.799772504</v>
+        <v>2968540.742370836</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3037473.0802058</v>
+        <v>3060924.300314213</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3129334.360639097</v>
+        <v>3153307.85825759</v>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>297.5151619680543</v>
+        <v>162.2190869336929</v>
       </c>
       <c r="B37" t="n">
-        <v>1585</v>
+        <v>2871</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1964.016054352688</v>
+        <v>2722.31350707809</v>
       </c>
       <c r="B38" t="n">
-        <v>2773</v>
+        <v>3440</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3630.516946737322</v>
+        <v>5282.407927222488</v>
       </c>
       <c r="B39" t="n">
-        <v>1970</v>
+        <v>1760</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5297.017839121956</v>
+        <v>7842.502347366885</v>
       </c>
       <c r="B40" t="n">
-        <v>1315</v>
+        <v>892</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6963.51873150659</v>
+        <v>10402.59676751128</v>
       </c>
       <c r="B41" t="n">
-        <v>764</v>
+        <v>454</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8630.019623891223</v>
+        <v>12962.69118765568</v>
       </c>
       <c r="B42" t="n">
-        <v>527</v>
+        <v>238</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>10296.52051627586</v>
+        <v>15522.78560780008</v>
       </c>
       <c r="B43" t="n">
-        <v>307</v>
+        <v>126</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>11963.02140866049</v>
+        <v>18082.88002794448</v>
       </c>
       <c r="B44" t="n">
-        <v>227</v>
+        <v>82</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>13629.52230104512</v>
+        <v>20642.97444808887</v>
       </c>
       <c r="B45" t="n">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15296.02319342976</v>
+        <v>23203.06886823327</v>
       </c>
       <c r="B46" t="n">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16962.52408581439</v>
+        <v>25763.16328837767</v>
       </c>
       <c r="B47" t="n">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>18629.02497819902</v>
+        <v>28323.25770852207</v>
       </c>
       <c r="B48" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>20295.52587058366</v>
+        <v>30883.35212866646</v>
       </c>
       <c r="B49" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>21962.02676296829</v>
+        <v>33443.44654881086</v>
       </c>
       <c r="B50" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>23628.52765535293</v>
+        <v>36003.54096895526</v>
       </c>
       <c r="B51" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>25295.02854773756</v>
+        <v>38563.63538909965</v>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>26961.52944012219</v>
+        <v>41123.72980924405</v>
       </c>
       <c r="B53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>28628.03033250683</v>
+        <v>43683.82422938845</v>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>30294.53122489146</v>
+        <v>46243.91864953285</v>
       </c>
       <c r="B55" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>31961.0321172761</v>
+        <v>48804.01306967725</v>
       </c>
       <c r="B56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>33627.53300966073</v>
+        <v>51364.10748982165</v>
       </c>
       <c r="B57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>35294.03390204536</v>
+        <v>53924.20190996604</v>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>36960.53479442999</v>
+        <v>56484.29633011044</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>38627.03568681463</v>
+        <v>59044.39075025484</v>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>40293.53657919927</v>
+        <v>61604.48517039923</v>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>41960.0374715839</v>
+        <v>64164.57959054363</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>43626.53836396853</v>
+        <v>66724.67401068803</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>45293.03925635316</v>
+        <v>69284.76843083242</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>46959.5401487378</v>
+        <v>71844.86285097683</v>
       </c>
       <c r="B65" t="n">
         <v>0</v>
@@ -1279,10 +1279,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>48626.04104112244</v>
+        <v>74404.95727112122</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>50292.54193350707</v>
+        <v>76965.05169126562</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>51959.0428258917</v>
+        <v>79525.14611141002</v>
       </c>
       <c r="B68" t="n">
         <v>0</v>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>53625.54371827633</v>
+        <v>82085.24053155442</v>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>55292.04461066097</v>
+        <v>84645.33495169881</v>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>56958.5455030456</v>
+        <v>87205.42937184322</v>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.3228204131684999</v>
+        <v>0.3646825108774885</v>
       </c>
       <c r="B72" t="n">
-        <v>7038</v>
+        <v>8392</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>37.35545444265147</v>
+        <v>59.94364952364113</v>
       </c>
       <c r="B73" t="n">
-        <v>1794</v>
+        <v>1106</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>74.38808847213444</v>
+        <v>119.5226165364048</v>
       </c>
       <c r="B74" t="n">
-        <v>610</v>
+        <v>285</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>111.4207225016174</v>
+        <v>179.1015835491684</v>
       </c>
       <c r="B75" t="n">
-        <v>214</v>
+        <v>101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>148.4533565311004</v>
+        <v>238.6805505619321</v>
       </c>
       <c r="B76" t="n">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>185.4859905605834</v>
+        <v>298.2595175746957</v>
       </c>
       <c r="B77" t="n">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>222.5186245900663</v>
+        <v>357.8384845874593</v>
       </c>
       <c r="B78" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>259.5512586195493</v>
+        <v>417.417451600223</v>
       </c>
       <c r="B79" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>296.5838926490322</v>
+        <v>476.9964186129866</v>
       </c>
       <c r="B80" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>333.6165266785152</v>
+        <v>536.5753856257503</v>
       </c>
       <c r="B81" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>370.6491607079982</v>
+        <v>596.154352638514</v>
       </c>
       <c r="B82" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>407.6817947374811</v>
+        <v>655.7333196512776</v>
       </c>
       <c r="B83" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>444.7144287669641</v>
+        <v>715.3122866640412</v>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>481.7470627964471</v>
+        <v>774.8912536768048</v>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>518.7796968259302</v>
+        <v>834.4702206895685</v>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>555.8123308554131</v>
+        <v>894.0491877023321</v>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>592.8449648848961</v>
+        <v>953.6281547150958</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>629.8775989143791</v>
+        <v>1013.207121727859</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>666.910232943862</v>
+        <v>1072.786088740623</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>703.942866973345</v>
+        <v>1132.365055753387</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>740.975501002828</v>
+        <v>1191.94402276615</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>778.0081350323109</v>
+        <v>1251.522989778914</v>
       </c>
       <c r="B93" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>815.0407690617939</v>
+        <v>1311.101956791678</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>852.0734030912769</v>
+        <v>1370.680923804441</v>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>889.1060371207598</v>
+        <v>1430.259890817205</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>926.1386711502428</v>
+        <v>1489.838857829968</v>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>963.1713051797258</v>
+        <v>1549.417824842732</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1000.203939209209</v>
+        <v>1608.996791855496</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1037.236573238692</v>
+        <v>1668.575758868259</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1074.269207268175</v>
+        <v>1728.154725881023</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1111.301841297658</v>
+        <v>1787.733692893787</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1148.334475327141</v>
+        <v>1847.31265990655</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1185.367109356624</v>
+        <v>1906.891626919314</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1222.399743386107</v>
+        <v>1966.470593932077</v>
       </c>
       <c r="B105" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1259.43237741559</v>
+        <v>2026.049560944841</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-3.260250812209071e+66</v>
+        <v>-1.166232486207181e+67</v>
       </c>
       <c r="B107" t="n">
         <v>1</v>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-3.166408640787946e+66</v>
+        <v>-1.097555566365475e+67</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-3.072566469366821e+66</v>
+        <v>-1.028878646523769e+67</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-2.978724297945696e+66</v>
+        <v>-9.602017266820622e+66</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-2.884882126524571e+66</v>
+        <v>-8.91524806840356e+66</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-2.791039955103446e+66</v>
+        <v>-8.228478869986497e+66</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-2.697197783682321e+66</v>
+        <v>-7.541709671569433e+66</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-2.603355612261196e+66</v>
+        <v>-6.85494047315237e+66</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-2.509513440840071e+66</v>
+        <v>-6.168171274735308e+66</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-2.415671269418946e+66</v>
+        <v>-5.481402076318245e+66</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-2.321829097997822e+66</v>
+        <v>-4.794632877901183e+66</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-2.227986926576696e+66</v>
+        <v>-4.107863679484119e+66</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-2.134144755155572e+66</v>
+        <v>-3.421094481067056e+66</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-2.040302583734447e+66</v>
+        <v>-2.734325282649994e+66</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-1.946460412313322e+66</v>
+        <v>-2.047556084232931e+66</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-1.852618240892197e+66</v>
+        <v>-1.360786885815869e+66</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-1.758776069471072e+66</v>
+        <v>-6.740176873988053e+65</v>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>9992</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-1.664933898049947e+66</v>
+        <v>1.275151101825808e+64</v>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-1.571091726628822e+66</v>
+        <v>6.9952070943532e+65</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-1.477249555207697e+66</v>
+        <v>1.386289907852383e+66</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>-1.383407383786572e+66</v>
+        <v>2.073059106269445e+66</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>-1.289565212365447e+66</v>
+        <v>2.759828304686509e+66</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,10 +2098,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>-1.195723040944322e+66</v>
+        <v>3.446597503103572e+66</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>-1.101880869523197e+66</v>
+        <v>4.133366701520635e+66</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>-1.008038698102072e+66</v>
+        <v>4.820135899937699e+66</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>-9.141965266809472e+65</v>
+        <v>5.506905098354759e+66</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-8.203543552598223e+65</v>
+        <v>6.193674296771823e+66</v>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-7.265121838386974e+65</v>
+        <v>6.880443495188886e+66</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>-6.326700124175725e+65</v>
+        <v>7.567212693605949e+66</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-5.388278409964472e+65</v>
+        <v>8.253981892023013e+66</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-4.449856695753223e+65</v>
+        <v>8.940751090440073e+66</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-3.511434981541975e+65</v>
+        <v>9.627520288857136e+66</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>-2.573013267330726e+65</v>
+        <v>1.03142894872742e+67</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>-1.634591553119477e+65</v>
+        <v>1.100105868569126e+67</v>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>-6.961698389082278e+64</v>
+        <v>1.168782788410833e+67</v>
       </c>
       <c r="B141" t="n">
-        <v>9997</v>
+        <v>1</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>

--- a/data_cripto/montecarlo_histograma.xlsx
+++ b/data_cripto/montecarlo_histograma.xlsx
@@ -447,10 +447,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12266.88818276355</v>
+        <v>5693.540322207515</v>
       </c>
       <c r="B2" t="n">
-        <v>2163</v>
+        <v>3584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -460,10 +460,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104650.4461261408</v>
+        <v>151898.9708515727</v>
       </c>
       <c r="B3" t="n">
-        <v>2888</v>
+        <v>3371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -473,10 +473,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>197034.004069518</v>
+        <v>298104.4013809378</v>
       </c>
       <c r="B4" t="n">
-        <v>1884</v>
+        <v>1496</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -486,10 +486,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>289417.5620128953</v>
+        <v>444309.8319103029</v>
       </c>
       <c r="B5" t="n">
-        <v>1104</v>
+        <v>733</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -499,10 +499,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>381801.1199562725</v>
+        <v>590515.2624396681</v>
       </c>
       <c r="B6" t="n">
-        <v>682</v>
+        <v>357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -512,10 +512,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>474184.6778996498</v>
+        <v>736720.6929690331</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>566568.2358430271</v>
+        <v>882926.1234983983</v>
       </c>
       <c r="B8" t="n">
-        <v>263</v>
+        <v>102</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>658951.7937864043</v>
+        <v>1029131.554027764</v>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -551,10 +551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>751335.3517297816</v>
+        <v>1175336.984557129</v>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -564,10 +564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>843718.9096731589</v>
+        <v>1321542.415086494</v>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>936102.4676165361</v>
+        <v>1467747.845615859</v>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1028486.025559913</v>
+        <v>1613953.276145224</v>
       </c>
       <c r="B13" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -603,10 +603,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1120869.583503291</v>
+        <v>1760158.706674589</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1213253.141446668</v>
+        <v>1906364.137203954</v>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -629,10 +629,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1305636.699390045</v>
+        <v>2052569.56773332</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -642,10 +642,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1398020.257333422</v>
+        <v>2198774.998262684</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1490403.815276799</v>
+        <v>2344980.42879205</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1582787.373220177</v>
+        <v>2491185.859321415</v>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1675170.931163554</v>
+        <v>2637391.28985078</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -694,10 +694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1767554.489106931</v>
+        <v>2783596.720380145</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1859938.047050308</v>
+        <v>2929802.15090951</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1952321.604993686</v>
+        <v>3076007.581438875</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2044705.162937063</v>
+        <v>3222213.011968241</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2137088.72088044</v>
+        <v>3368418.442497605</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -759,10 +759,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2229472.278823818</v>
+        <v>3514623.873026971</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2321855.836767195</v>
+        <v>3660829.303556336</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2414239.394710572</v>
+        <v>3807034.734085701</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2506622.952653949</v>
+        <v>3953240.164615066</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2599006.510597326</v>
+        <v>4099445.595144432</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
@@ -824,10 +824,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2691390.068540704</v>
+        <v>4245651.025673797</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2783773.626484081</v>
+        <v>4391856.456203162</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2876157.184427458</v>
+        <v>4538061.886732527</v>
       </c>
       <c r="B33" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2968540.742370836</v>
+        <v>4684267.317261892</v>
       </c>
       <c r="B34" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3060924.300314213</v>
+        <v>4830472.747791258</v>
       </c>
       <c r="B35" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3153307.85825759</v>
+        <v>4976678.178320623</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>162.2190869336929</v>
+        <v>234.0326757837597</v>
       </c>
       <c r="B37" t="n">
-        <v>2871</v>
+        <v>1333</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -915,10 +915,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2722.31350707809</v>
+        <v>1796.322501512086</v>
       </c>
       <c r="B38" t="n">
-        <v>3440</v>
+        <v>2652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>5282.407927222488</v>
+        <v>3358.612327240413</v>
       </c>
       <c r="B39" t="n">
-        <v>1760</v>
+        <v>2019</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7842.502347366885</v>
+        <v>4920.90215296874</v>
       </c>
       <c r="B40" t="n">
-        <v>892</v>
+        <v>1378</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10402.59676751128</v>
+        <v>6483.191978697067</v>
       </c>
       <c r="B41" t="n">
-        <v>454</v>
+        <v>844</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>12962.69118765568</v>
+        <v>8045.481804425393</v>
       </c>
       <c r="B42" t="n">
-        <v>238</v>
+        <v>563</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -980,10 +980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>15522.78560780008</v>
+        <v>9607.771630153718</v>
       </c>
       <c r="B43" t="n">
-        <v>126</v>
+        <v>357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>18082.88002794448</v>
+        <v>11170.06145588205</v>
       </c>
       <c r="B44" t="n">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>20642.97444808887</v>
+        <v>12732.35128161037</v>
       </c>
       <c r="B45" t="n">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>23203.06886823327</v>
+        <v>14294.6411073387</v>
       </c>
       <c r="B46" t="n">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>25763.16328837767</v>
+        <v>15856.93093306703</v>
       </c>
       <c r="B47" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>28323.25770852207</v>
+        <v>17419.22075879535</v>
       </c>
       <c r="B48" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1058,10 +1058,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>30883.35212866646</v>
+        <v>18981.51058452368</v>
       </c>
       <c r="B49" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>33443.44654881086</v>
+        <v>20543.80041025201</v>
       </c>
       <c r="B50" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>36003.54096895526</v>
+        <v>22106.09023598033</v>
       </c>
       <c r="B51" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>38563.63538909965</v>
+        <v>23668.38006170866</v>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>41123.72980924405</v>
+        <v>25230.66988743699</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>43683.82422938845</v>
+        <v>26792.95971316531</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>46243.91864953285</v>
+        <v>28355.24953889364</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>48804.01306967725</v>
+        <v>29917.53936462197</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>51364.10748982165</v>
+        <v>31479.82919035029</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>53924.20190996604</v>
+        <v>33042.11901607862</v>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>56484.29633011044</v>
+        <v>34604.40884180694</v>
       </c>
       <c r="B59" t="n">
         <v>1</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59044.39075025484</v>
+        <v>36166.69866753527</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>61604.48517039923</v>
+        <v>37728.9884932636</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>64164.57959054363</v>
+        <v>39291.27831899193</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>66724.67401068803</v>
+        <v>40853.56814472025</v>
       </c>
       <c r="B63" t="n">
         <v>0</v>
@@ -1253,10 +1253,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>69284.76843083242</v>
+        <v>42415.85797044858</v>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>71844.86285097683</v>
+        <v>43978.14779617691</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>74404.95727112122</v>
+        <v>45540.43762190524</v>
       </c>
       <c r="B66" t="n">
         <v>0</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>76965.05169126562</v>
+        <v>47102.72744763356</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>79525.14611141002</v>
+        <v>48665.01727336189</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>82085.24053155442</v>
+        <v>50227.30709909021</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>84645.33495169881</v>
+        <v>51789.59692481854</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>87205.42937184322</v>
+        <v>53351.88675054687</v>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.3646825108774885</v>
+        <v>0.4801441493547836</v>
       </c>
       <c r="B72" t="n">
-        <v>8392</v>
+        <v>6545</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>59.94364952364113</v>
+        <v>31.54834697048042</v>
       </c>
       <c r="B73" t="n">
-        <v>1106</v>
+        <v>2028</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119.5226165364048</v>
+        <v>62.61654979160607</v>
       </c>
       <c r="B74" t="n">
-        <v>285</v>
+        <v>686</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>179.1015835491684</v>
+        <v>93.68475261273171</v>
       </c>
       <c r="B75" t="n">
-        <v>101</v>
+        <v>330</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>238.6805505619321</v>
+        <v>124.7529554338574</v>
       </c>
       <c r="B76" t="n">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>298.2595175746957</v>
+        <v>155.821158254983</v>
       </c>
       <c r="B77" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>357.8384845874593</v>
+        <v>186.8893610761086</v>
       </c>
       <c r="B78" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>417.417451600223</v>
+        <v>217.9575638972343</v>
       </c>
       <c r="B79" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>476.9964186129866</v>
+        <v>249.0257667183599</v>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>536.5753856257503</v>
+        <v>280.0939695394856</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>596.154352638514</v>
+        <v>311.1621723606112</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>655.7333196512776</v>
+        <v>342.2303751817368</v>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>715.3122866640412</v>
+        <v>373.2985780028625</v>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>774.8912536768048</v>
+        <v>404.3667808239881</v>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>834.4702206895685</v>
+        <v>435.4349836451137</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>894.0491877023321</v>
+        <v>466.5031864662394</v>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>953.6281547150958</v>
+        <v>497.571389287365</v>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1013.207121727859</v>
+        <v>528.6395921084908</v>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1072.786088740623</v>
+        <v>559.7077949296164</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1132.365055753387</v>
+        <v>590.775997750742</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1191.94402276615</v>
+        <v>621.8442005718676</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1251.522989778914</v>
+        <v>652.9124033929933</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1311.101956791678</v>
+        <v>683.9806062141189</v>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1370.680923804441</v>
+        <v>715.0488090352446</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1430.259890817205</v>
+        <v>746.1170118563703</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1489.838857829968</v>
+        <v>777.1852146774959</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1549.417824842732</v>
+        <v>808.2534174986215</v>
       </c>
       <c r="B98" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1608.996791855496</v>
+        <v>839.3216203197471</v>
       </c>
       <c r="B99" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1668.575758868259</v>
+        <v>870.3898231408727</v>
       </c>
       <c r="B100" t="n">
         <v>0</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1728.154725881023</v>
+        <v>901.4580259619985</v>
       </c>
       <c r="B101" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1787.733692893787</v>
+        <v>932.5262287831241</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1847.31265990655</v>
+        <v>963.5944316042497</v>
       </c>
       <c r="B103" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1906.891626919314</v>
+        <v>994.6626344253754</v>
       </c>
       <c r="B104" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1966.470593932077</v>
+        <v>1025.730837246501</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2026.049560944841</v>
+        <v>1056.799040067627</v>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>-1.166232486207181e+67</v>
+        <v>-1.253930288348395e+64</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>-1.097555566365475e+67</v>
+        <v>9.391964164904076e+69</v>
       </c>
       <c r="B108" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-1.028878646523769e+67</v>
+        <v>1.878394086911103e+70</v>
       </c>
       <c r="B109" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-9.602017266820622e+66</v>
+        <v>2.8175917573318e+70</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>-8.91524806840356e+66</v>
+        <v>3.756789427752496e+70</v>
       </c>
       <c r="B111" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-8.228478869986497e+66</v>
+        <v>4.695987098173191e+70</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>-7.541709671569433e+66</v>
+        <v>5.635184768593888e+70</v>
       </c>
       <c r="B113" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-6.85494047315237e+66</v>
+        <v>6.574382439014583e+70</v>
       </c>
       <c r="B114" t="n">
         <v>0</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-6.168171274735308e+66</v>
+        <v>7.513580109435279e+70</v>
       </c>
       <c r="B115" t="n">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>-5.481402076318245e+66</v>
+        <v>8.452777779855976e+70</v>
       </c>
       <c r="B116" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-4.794632877901183e+66</v>
+        <v>9.391975450276671e+70</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-4.107863679484119e+66</v>
+        <v>1.033117312069737e+71</v>
       </c>
       <c r="B118" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>-3.421094481067056e+66</v>
+        <v>1.127037079111806e+71</v>
       </c>
       <c r="B119" t="n">
         <v>0</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>-2.734325282649994e+66</v>
+        <v>1.220956846153876e+71</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-2.047556084232931e+66</v>
+        <v>1.314876613195945e+71</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>-1.360786885815869e+66</v>
+        <v>1.408796380238015e+71</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-6.740176873988053e+65</v>
+        <v>1.502716147280085e+71</v>
       </c>
       <c r="B123" t="n">
-        <v>9992</v>
+        <v>0</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1.275151101825808e+64</v>
+        <v>1.596635914322154e+71</v>
       </c>
       <c r="B124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>6.9952070943532e+65</v>
+        <v>1.690555681364224e+71</v>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1.386289907852383e+66</v>
+        <v>1.784475448406294e+71</v>
       </c>
       <c r="B126" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2.073059106269445e+66</v>
+        <v>1.878395215448363e+71</v>
       </c>
       <c r="B127" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2.759828304686509e+66</v>
+        <v>1.972314982490433e+71</v>
       </c>
       <c r="B128" t="n">
         <v>0</v>
@@ -2098,10 +2098,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3.446597503103572e+66</v>
+        <v>2.066234749532502e+71</v>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4.133366701520635e+66</v>
+        <v>2.160154516574572e+71</v>
       </c>
       <c r="B130" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>4.820135899937699e+66</v>
+        <v>2.254074283616641e+71</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>5.506905098354759e+66</v>
+        <v>2.347994050658711e+71</v>
       </c>
       <c r="B132" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>6.193674296771823e+66</v>
+        <v>2.44191381770078e+71</v>
       </c>
       <c r="B133" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>6.880443495188886e+66</v>
+        <v>2.53583358474285e+71</v>
       </c>
       <c r="B134" t="n">
         <v>0</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>7.567212693605949e+66</v>
+        <v>2.629753351784919e+71</v>
       </c>
       <c r="B135" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>8.253981892023013e+66</v>
+        <v>2.723673118826989e+71</v>
       </c>
       <c r="B136" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>8.940751090440073e+66</v>
+        <v>2.817592885869059e+71</v>
       </c>
       <c r="B137" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>9.627520288857136e+66</v>
+        <v>2.911512652911128e+71</v>
       </c>
       <c r="B138" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1.03142894872742e+67</v>
+        <v>3.005432419953198e+71</v>
       </c>
       <c r="B139" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1.100105868569126e+67</v>
+        <v>3.099352186995268e+71</v>
       </c>
       <c r="B140" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1.168782788410833e+67</v>
+        <v>3.193271954037337e+71</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>
